--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
+  <autoFilter ref="A1:P13"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+          <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
+          <t>Mantenimiento de transformador de potencia.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [9301] SAN ANTONIO.</t>
+          <t>SET : [7] CHALLAPAMPA.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,94 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+          <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-SÁBADO, 05 DE SETIEMBRE DE 2026:
-Circuito : [9301] SAN ANTONIO.
-Hora : 06:00 a 18:00 Hrs.
-Motivo : Mantenimiento del transformador de la subestación de Caylloma.
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 02/09/2026 17:58 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026 17:58</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6013&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>87cae465b632a656491c44ae0cc47040622c28e945e4feb4714ea9c02b51d013</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6029</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de transformador de potencia.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SET : [7] CHALLAPAMPA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 06 DE SETIEMBRE DE 2026:
@@ -736,30 +652,919 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:14</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Asentamiento E5 parcela 54 (Distrito de Majes).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de la</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 6388.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 08 DE SETIEMBRE DE 2026.
+Circuito : SED 6388.
+Hora : 07:00 a 10:00 Hrs.
+Motivo : Cambio de transformador de la SED.
+Zonas afectadas: Asentamiento E5 parcela 54 (Distrito de Majes).</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
+          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026 18:14</t>
+          <t>07/09/2026 9:13</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6030&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
+          <t>1d71bceff04af6c8fc99cfd29e208c83b00ab4b0d48c89ddfa64b38c2b79b710</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones de distrito de Cerro Colorado: Jose Luis Bustamante y Rivero Sector V.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde CC - 080311.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4422, 4421, 4432, 4420, 4829, 4433.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 08 DE SETIEMBRE DE 2026:
+Circuito : P. Yura desde CC - 080311.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones de distrito de Cerro Colorado: Jose Luis Bustamante y Rivero Sector V.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4422, 4421, 4432, 4420, 4829, 4433.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:19 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:19</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6040&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3bf6d23ecf5beea54ea04560e40f396f783c653feb053241fbb451ba61a5465b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6031</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Asentamiento E5 parcela 80 (Distrito de Majes).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de la</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 6384.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 08 DE SETIEMBRE DE 2026.
+Circuito : SED 6384.
+Hora : 10:00 a 13:00 Hrs.
+Motivo : Cambio de transformador de la SED.
+Zonas afectadas: Asentamiento E5 parcela 80 (Distrito de Majes).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:13</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6031&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9ee0b7f206ed2b45cc36be0673846dc1c838b50969096890a4e36a66eaaf4703</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Asentamiento E5 parcela 70 (Distrito de Majes).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de la</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 6386.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 08 DE SETIEMBRE DE 2026.
+Circuito : SED 6386.
+Hora : 13:00 a 16:00 Hrs.
+Motivo : Cambio de transformador de la SED.
+Zonas afectadas: Asentamiento E5 parcela 70 (Distrito de Majes).</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:13</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6032&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>02a059a8945c9fb117d3c14dedb1e879f0f912529b54d006490c24d220acbdd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pionero II desde CC - 200103.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7906, 7907, 7908, 7909, 7910, 8964.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
+Circuito : Pionero II desde CC - 200103.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7906, 7907, 7908, 7909, 7910, 8964.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:16</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6036&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8ad500afec351b1d964efb4c7492a8cb6b855378f9b1c402c81a23d955489fd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Inclan desde SF6-3 - 200144.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
+Circuito : Inclan desde SF6-3 - 200144.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de subestaciones de distribución.
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Miramar.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:16</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6035&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6ae85a95ef67f87f41c9342eb0e90c52f6a3c0daa3307d1fc5bf929a220618e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6037</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 50 KVA.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2932.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
+Circuito : SED 2932.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador a 50 KVA.
+Zonas afectadas: Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:17</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6037&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>ca582210034eee497612762935a77a5f86682851ebb78a9f5c208d26adfda11e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6038</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 100 KVA.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3995.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
+Circuito : SED 3995.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador a 100 KVA.
+Zonas afectadas: Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:17</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6038&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8dab1a4ebef2c2c14bbb52adf8341645b707401bb3aac092e959afa5104906ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6039</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde SF6 - 200190.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 10 DE SETIEMBRE DE 2026:
+Circuito : P. Yura desde SF6 - 200190.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:18 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:18</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6039&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>87fe765313957042a787a32d6887a111ca456de676ca1f9c472a83ff928870f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6033</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, de La Joya</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Cruce la Joya lateral 1 (Distrito de La Joya).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de la</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 6802.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 10 DE SETIEMBRE DE 2026.
+Circuito : SED 6802.
+Hora : 09:00 a 12:00 Hrs.
+Motivo : Cambio de transformador de la SED.
+Zonas afectadas: Cruce la Joya lateral 1 (Distrito de La Joya).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:14</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6033&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>cf8827911541f79329effdfd8a48630dd4ac1bbd7a4962a5ea12f789cb2a22d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6034</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, de La Joya</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Irrigación San camilo Zona A (Distrito de La Joya).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de la</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 6902.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 10 DE SETIEMBRE DE 2026.
+Circuito : SED 6902.
+Hora : 14:00 a 17:00 Hrs.
+Motivo : Cambio de transformador de la SED.
+Zonas afectadas: Irrigación San camilo Zona A (Distrito de La Joya).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026 9:14</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6034&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2f4b11402f87df505f05ddf61b3f0aefa5794236bde4fb06dbfd6630463a1704</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -800,7 +1605,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:42:00</t>
+          <t>2026-09-07 15:53:55</t>
         </is>
       </c>
     </row>
@@ -824,7 +1629,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -836,7 +1641,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -848,7 +1653,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -896,7 +1701,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -908,7 +1713,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -920,7 +1725,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -947,7 +1752,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
-  <autoFilter ref="A1:P13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
+          <t>Asentamiento E5 parcela 54 (Distrito de Majes).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de transformador de potencia.</t>
+          <t>Cambio de transformador de la</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET : [7] CHALLAPAMPA.</t>
+          <t>Circuito : SED 6388.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,92 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 06 DE SETIEMBRE DE 2026:
-SET : [7] CHALLAPAMPA.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de transformador de potencia.
-Zonas afectadas: Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026 18:14</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6030</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Asentamiento E5 parcela 54 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de la</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 6388.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 08 DE SETIEMBRE DE 2026.
@@ -731,80 +647,80 @@
 Zonas afectadas: Asentamiento E5 parcela 54 (Distrito de Majes).</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:13</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6030&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>1d71bceff04af6c8fc99cfd29e208c83b00ab4b0d48c89ddfa64b38c2b79b710</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6040</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Cerro Colorado: Jose Luis Bustamante y Rivero Sector V.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde CC - 080311.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4422, 4421, 4432, 4420, 4829, 4433.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 08 DE SETIEMBRE DE 2026:
@@ -815,76 +731,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4422, 4421, 4432, 4420, 4829, 4433.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:19</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6040&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>3bf6d23ecf5beea54ea04560e40f396f783c653feb053241fbb451ba61a5465b</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6031</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Asentamiento E5 parcela 80 (Distrito de Majes).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6384.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 08 DE SETIEMBRE DE 2026.
@@ -894,76 +810,76 @@
 Zonas afectadas: Asentamiento E5 parcela 80 (Distrito de Majes).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:13</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6031&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>9ee0b7f206ed2b45cc36be0673846dc1c838b50969096890a4e36a66eaaf4703</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6032</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Asentamiento E5 parcela 70 (Distrito de Majes).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6386.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 08 DE SETIEMBRE DE 2026.
@@ -973,80 +889,80 @@
 Zonas afectadas: Asentamiento E5 parcela 70 (Distrito de Majes).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:13</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6032&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>02a059a8945c9fb117d3c14dedb1e879f0f912529b54d006490c24d220acbdd8</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6036</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pionero II desde CC - 200103.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7906, 7907, 7908, 7909, 7910, 8964.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
@@ -1057,80 +973,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7906, 7907, 7908, 7909, 7910, 8964.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:16</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6036&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>8ad500afec351b1d964efb4c7492a8cb6b855378f9b1c402c81a23d955489fd2</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6035</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Inclan desde SF6-3 - 200144.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
@@ -1141,76 +1057,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:16</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6035&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>6ae85a95ef67f87f41c9342eb0e90c52f6a3c0daa3307d1fc5bf929a220618e6</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6037</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 50 KVA.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2932.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
@@ -1220,76 +1136,76 @@
 Zonas afectadas: Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:17</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6037&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ca582210034eee497612762935a77a5f86682851ebb78a9f5c208d26adfda11e</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6038</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100 KVA.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3995.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
@@ -1299,80 +1215,80 @@
 Zonas afectadas: Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:17</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6038&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>8dab1a4ebef2c2c14bbb52adf8341645b707401bb3aac092e959afa5104906ba</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde SF6 - 200190.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026:
@@ -1383,76 +1299,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:18</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6039&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>87fe765313957042a787a32d6887a111ca456de676ca1f9c472a83ff928870f4</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6033</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6802.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1462,76 +1378,76 @@
 Zonas afectadas: Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6033&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>cf8827911541f79329effdfd8a48630dd4ac1bbd7a4962a5ea12f789cb2a22d0</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6034</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6902.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1541,30 +1457,30 @@
 Zonas afectadas: Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6034&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2f4b11402f87df505f05ddf61b3f0aefa5794236bde4fb06dbfd6630463a1704</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1605,7 +1521,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 15:53:55</t>
+          <t>2026-09-08 14:36:01</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1545,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1557,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1569,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1641,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1668,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P16" headerRowCount="1">
+  <autoFilter ref="A1:P16"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1479,8 +1479,345 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pionero II desde CC - 200194.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 11 DE SETIEMBRE DE 2026:
+Circuito : Pionero II desde CC - 200194.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de subestaciones de distribución).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 17:07</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6042&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8ef2a9b3c831ad367b75bd5a413da3061ec767bf0221251a968ef977a88b0dd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6043</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Aplao, de Aplao</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde CC - 810103.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 11 DE SETIEMBRE DE 2026:
+Circuito : Corire desde CC - 810103.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 17:07</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6043&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>7da6e65cf9cffad256f55090ee3ff48c5b5c7b18dd8fce2efb123d6f7fc571ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Callalli, San Antonio de Chuca, Yanque, de Callalli, de San Antonio de Chuca, de Yanque</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [9103] IMATA.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 11 DE SETIEMBRE DE 2026:
+Circuito : [9103] IMATA.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).
+Zonas afectadas: Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 08/09/2026 17:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 17:08</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6044&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>a55476c7beee0678c20231f54b156b56e105abd07e79d8633f14ccd6c39c75cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cocachacra, de Cocachacra</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 13 DE SETIEMBRE DE 2026:
+LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi.
+SET : [38] CHUCARAPI Y [39] COCACHACRA.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de la Línea de Transmisión y el transformador.
+Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026 17:06</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1521,7 +1858,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 14:36:01</t>
+          <t>2026-09-09 14:38:56</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1882,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1894,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1906,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1954,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1966,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1978,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1668,7 +2005,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P16" headerRowCount="1">
-  <autoFilter ref="A1:P16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Asentamiento E5 parcela 54 (Distrito de Majes).</t>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador de la</t>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 6388.</t>
+          <t>Circuito : Pionero II desde CC - 200103.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,333 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7906, 7907, 7908, 7909, 7910, 8964.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 08 DE SETIEMBRE DE 2026.
-Circuito : SED 6388.
-Hora : 07:00 a 10:00 Hrs.
-Motivo : Cambio de transformador de la SED.
-Zonas afectadas: Asentamiento E5 parcela 54 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:13</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6030&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>1d71bceff04af6c8fc99cfd29e208c83b00ab4b0d48c89ddfa64b38c2b79b710</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6040</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones de distrito de Cerro Colorado: Jose Luis Bustamante y Rivero Sector V.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde CC - 080311.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4422, 4421, 4432, 4420, 4829, 4433.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 08 DE SETIEMBRE DE 2026:
-Circuito : P. Yura desde CC - 080311.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones de distrito de Cerro Colorado: Jose Luis Bustamante y Rivero Sector V.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4422, 4421, 4432, 4420, 4829, 4433.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:19 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:19</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6040&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>3bf6d23ecf5beea54ea04560e40f396f783c653feb053241fbb451ba61a5465b</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6031</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Asentamiento E5 parcela 80 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de la</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 6384.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 08 DE SETIEMBRE DE 2026.
-Circuito : SED 6384.
-Hora : 10:00 a 13:00 Hrs.
-Motivo : Cambio de transformador de la SED.
-Zonas afectadas: Asentamiento E5 parcela 80 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:13</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6031&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9ee0b7f206ed2b45cc36be0673846dc1c838b50969096890a4e36a66eaaf4703</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Asentamiento E5 parcela 70 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de la</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 6386.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 08 DE SETIEMBRE DE 2026.
-Circuito : SED 6386.
-Hora : 13:00 a 16:00 Hrs.
-Motivo : Cambio de transformador de la SED.
-Zonas afectadas: Asentamiento E5 parcela 70 (Distrito de Majes).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:13 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:13</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6032&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>02a059a8945c9fb117d3c14dedb1e879f0f912529b54d006490c24d220acbdd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6036</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pionero II desde CC - 200103.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7906, 7907, 7908, 7909, 7910, 8964.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
@@ -973,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7906, 7907, 7908, 7909, 7910, 8964.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:16</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6036&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>8ad500afec351b1d964efb4c7492a8cb6b855378f9b1c402c81a23d955489fd2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6035</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Inclan desde SF6-3 - 200144.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
@@ -1057,76 +736,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:16</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6035&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>6ae85a95ef67f87f41c9342eb0e90c52f6a3c0daa3307d1fc5bf929a220618e6</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6037</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 50 KVA.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2932.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
@@ -1136,76 +815,76 @@
 Zonas afectadas: Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:17</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6037&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ca582210034eee497612762935a77a5f86682851ebb78a9f5c208d26adfda11e</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6038</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100 KVA.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3995.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
@@ -1215,80 +894,80 @@
 Zonas afectadas: Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:17</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6038&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>8dab1a4ebef2c2c14bbb52adf8341645b707401bb3aac092e959afa5104906ba</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde SF6 - 200190.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026:
@@ -1299,76 +978,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:18</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6039&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>87fe765313957042a787a32d6887a111ca456de676ca1f9c472a83ff928870f4</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6033</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6802.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1378,76 +1057,76 @@
 Zonas afectadas: Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6033&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>cf8827911541f79329effdfd8a48630dd4ac1bbd7a4962a5ea12f789cb2a22d0</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6034</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6902.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1457,80 +1136,80 @@
 Zonas afectadas: Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6034&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2f4b11402f87df505f05ddf61b3f0aefa5794236bde4fb06dbfd6630463a1704</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6042</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pionero II desde CC - 200194.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1541,80 +1220,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6042&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>8ef2a9b3c831ad367b75bd5a413da3061ec767bf0221251a968ef977a88b0dd2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6043</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Aplao, de Aplao</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810103.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1625,80 +1304,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6043&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>7da6e65cf9cffad256f55090ee3ff48c5b5c7b18dd8fce2efb123d6f7fc571ec</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6044</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Callalli, San Antonio de Chuca, Yanque, de Callalli, de San Antonio de Chuca, de Yanque</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9103] IMATA.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1709,80 +1388,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:08</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6044&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>a55476c7beee0678c20231f54b156b56e105abd07e79d8633f14ccd6c39c75cd</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6041</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -1794,30 +1473,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:06</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P16"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1858,7 +1537,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:38:56</t>
+          <t>2026-09-10 14:29:19</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1561,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1573,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1585,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1657,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2005,7 +1684,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).</t>
+          <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pionero II desde CC - 200103.</t>
+          <t>Circuito : P. Yura desde SF6 - 200190.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,336 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7906, 7907, 7908, 7909, 7910, 8964.</t>
+          <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
-Circuito : Pionero II desde CC - 200103.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, otros mantenimientos).
-Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Sector C-2.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7906, 7907, 7908, 7909, 7910, 8964.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:16</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6036&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>8ad500afec351b1d964efb4c7492a8cb6b855378f9b1c402c81a23d955489fd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6035</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Inclan desde SF6-3 - 200144.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 09 DE SETIEMBRE DE 2026:
-Circuito : Inclan desde SF6-3 - 200144.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de subestaciones de distribución.
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Miramar.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:16 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:16</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6035&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>6ae85a95ef67f87f41c9342eb0e90c52f6a3c0daa3307d1fc5bf929a220618e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6037</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 50 KVA.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2932.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
-Circuito : SED 2932.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador a 50 KVA.
-Zonas afectadas: Mz. F-G-N-M zona 1 de Urb. Francisco Garcia Calderon (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:17</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6037&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>ca582210034eee497612762935a77a5f86682851ebb78a9f5c208d26adfda11e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100 KVA.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3995.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 09 DE SETIEMBRE DE 2026.
-Circuito : SED 3995.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador a 100 KVA.
-Zonas afectadas: Zona 4 de Urb. Asociación Las Flores (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:17 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:17</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6038&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8dab1a4ebef2c2c14bbb52adf8341645b707401bb3aac092e959afa5104906ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6039</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde SF6 - 200190.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026:
@@ -978,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:18</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6039&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>87fe765313957042a787a32d6887a111ca456de676ca1f9c472a83ff928870f4</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6033</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6802.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1057,76 +731,76 @@
 Zonas afectadas: Cruce la Joya lateral 1 (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6033&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>cf8827911541f79329effdfd8a48630dd4ac1bbd7a4962a5ea12f789cb2a22d0</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6034</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de la</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 6902.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 10 DE SETIEMBRE DE 2026.
@@ -1136,80 +810,80 @@
 Zonas afectadas: Irrigación San camilo Zona A (Distrito de La Joya).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>07/09/2026 9:14</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6034&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2f4b11402f87df505f05ddf61b3f0aefa5794236bde4fb06dbfd6630463a1704</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6042</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pionero II desde CC - 200194.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1220,80 +894,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6042&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>8ef2a9b3c831ad367b75bd5a413da3061ec767bf0221251a968ef977a88b0dd2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6043</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Aplao, de Aplao</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810103.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1304,80 +978,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6043&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>7da6e65cf9cffad256f55090ee3ff48c5b5c7b18dd8fce2efb123d6f7fc571ec</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6044</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Callalli, San Antonio de Chuca, Yanque, de Callalli, de San Antonio de Chuca, de Yanque</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9103] IMATA.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1388,80 +1062,164 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:08</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6044&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>a55476c7beee0678c20231f54b156b56e105abd07e79d8633f14ccd6c39c75cd</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Maca, de Maca</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Maca: Maca.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de estructuras de media tensión.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Callalli 22.9 desde CC - 910131.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7526, 7543, 7527.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 13 DE SETIEMBRE DE 2026:
+Circuito : Callalli 22.9 desde CC - 910131.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Cambio de estructuras de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Maca: Maca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7526, 7543, 7527.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 10/09/2026 15:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 15:00</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6045&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>14d454a780bb8f5a7932546cbe280cd936bdcfb735648235bdc4ca79b20e0121</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6041</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -1473,30 +1231,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:06</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1537,7 +1295,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:29:19</t>
+          <t>2026-09-11 14:28:42</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1319,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1331,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1343,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1391,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1403,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1415,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1442,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.</t>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : P. Yura desde SF6 - 200190.</t>
+          <t>Circuito : Pionero II desde CC - 200194.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,252 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
+          <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 10 DE SETIEMBRE DE 2026:
-Circuito : P. Yura desde SF6 - 200190.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Bio Huerto Virgen de Copacabana, La Cabaña.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4705, 4704, 4706, 4707, 4708, 5357, 5358, 5359, 5538, 5539, 10170, 5866, 5653, 5965, 5867, 5868, 5654, 5983, 5986, 5987, 5984, 5985.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:18 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:18</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6039&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>87fe765313957042a787a32d6887a111ca456de676ca1f9c472a83ff928870f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6033</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>La Joya, de La Joya</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Cruce la Joya lateral 1 (Distrito de La Joya).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de la</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 6802.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 10 DE SETIEMBRE DE 2026.
-Circuito : SED 6802.
-Hora : 09:00 a 12:00 Hrs.
-Motivo : Cambio de transformador de la SED.
-Zonas afectadas: Cruce la Joya lateral 1 (Distrito de La Joya).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:14</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6033&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>cf8827911541f79329effdfd8a48630dd4ac1bbd7a4962a5ea12f789cb2a22d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6034</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>La Joya, de La Joya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Irrigación San camilo Zona A (Distrito de La Joya).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de la</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 6902.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 10 DE SETIEMBRE DE 2026.
-Circuito : SED 6902.
-Hora : 14:00 a 17:00 Hrs.
-Motivo : Cambio de transformador de la SED.
-Zonas afectadas: Irrigación San camilo Zona A (Distrito de La Joya).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 07/09/2026 9:14 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 9:14</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6034&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2f4b11402f87df505f05ddf61b3f0aefa5794236bde4fb06dbfd6630463a1704</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pionero II desde CC - 200194.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -894,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6042&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>8ef2a9b3c831ad367b75bd5a413da3061ec767bf0221251a968ef977a88b0dd2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6043</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Aplao, de Aplao</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810103.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -978,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:07</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6043&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>7da6e65cf9cffad256f55090ee3ff48c5b5c7b18dd8fce2efb123d6f7fc571ec</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6044</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Callalli, San Antonio de Chuca, Yanque, de Callalli, de San Antonio de Chuca, de Yanque</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9103] IMATA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 11 DE SETIEMBRE DE 2026:
@@ -1062,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:08</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6044&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>a55476c7beee0678c20231f54b156b56e105abd07e79d8633f14ccd6c39c75cd</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6045</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Maca, de Maca</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Maca: Maca.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de estructuras de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC - 910131.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7526, 7543, 7527.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -1146,80 +904,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7526, 7543, 7527.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/09/2026 15:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/09/2026 15:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6045&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>14d454a780bb8f5a7932546cbe280cd936bdcfb735648235bdc4ca79b20e0121</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6041</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -1231,30 +989,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:06</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1295,7 +1053,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:28:42</t>
+          <t>2026-09-12 13:37:50</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1077,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1089,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1101,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1173,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1200,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Maca, de Maca</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.</t>
+          <t>Urbanizaciones del distrito de Maca: Maca.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de</t>
+          <t>Cambio de estructuras de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pionero II desde CC - 200194.</t>
+          <t>Circuito : Callalli 22.9 desde CC - 910131.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,262 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
+          <t>7526, 7543, 7527.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 11 DE SETIEMBRE DE 2026:
-Circuito : Pionero II desde CC - 200194.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, mantenimiento de subestaciones de distribución).
-Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G Sector 1.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8810, 8811, 7997, 8519, 8520, 8521, 8775, 8773, 8774, 8772, 8771.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026 17:07</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6042&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>8ef2a9b3c831ad367b75bd5a413da3061ec767bf0221251a968ef977a88b0dd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6043</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Aplao, de Aplao</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde CC - 810103.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 11 DE SETIEMBRE DE 2026:
-Circuito : Corire desde CC - 810103.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (Cambio de transformador, cambio de crucetas, cambio de EMT, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Aplao: Ampliación El Castillo I Etapa, El Castillo, El Colorado.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7022, 7026, 7355, 7025, 7196, 7024, 7023, 7027, 7192, 7485, 7028, 7944, 8947, 8564, 8563.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 08/09/2026 17:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026 17:07</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6043&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>7da6e65cf9cffad256f55090ee3ff48c5b5c7b18dd8fce2efb123d6f7fc571ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Callalli, San Antonio de Chuca, Yanque, de Callalli, de San Antonio de Chuca, de Yanque</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [9103] IMATA.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 11 DE SETIEMBRE DE 2026:
-Circuito : [9103] IMATA.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión (Cambio de pararrayos, instalación de recloser).
-Zonas afectadas: Urbanizaciones del distrito de Callalli: Pulpera. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estacion Pillones, Imata. Urbanizaciones del distrito de Yanque: Chalhuanca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7551, 7552, 7553, 7558, 7550, 7557, 7555, 7556, 7587, 7591, 7600, 7711, 7828, 7834, 9374, 9376, 9396, 7554, 7589.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 08/09/2026 17:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026 17:08</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6044&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>a55476c7beee0678c20231f54b156b56e105abd07e79d8633f14ccd6c39c75cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Maca, de Maca</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Maca: Maca.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de estructuras de media tensión.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Callalli 22.9 desde CC - 910131.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7526, 7543, 7527.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -904,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7526, 7543, 7527.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/09/2026 15:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/09/2026 15:00</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6045&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>14d454a780bb8f5a7932546cbe280cd936bdcfb735648235bdc4ca79b20e0121</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6041</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 13 DE SETIEMBRE DE 2026:
@@ -989,30 +737,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>08/09/2026 17:06</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1053,7 +801,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:37:50</t>
+          <t>2026-09-13 14:26:38</t>
         </is>
       </c>
     </row>
@@ -1077,7 +825,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1089,7 +837,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1101,7 +849,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1173,7 +921,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1200,7 +948,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -759,8 +759,512 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pionero II desde CC - 200462.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 15 DE SETIEMBRE DE 2026:
+Circuito : Pionero II desde CC - 200462.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:07</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6047&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4802647c0980302585f6b7cb04cdc5fb85c2623530cb3eb2ae7abc5c211dc753</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6048</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Huancarqui, de Huancarqui</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Huancarqui: Pampa Blanca, Tomaca.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, poda de árboles).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde BC - 810113.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 15 DE SETIEMBRE DE 2026:
+Circuito : Corire desde BC - 810113.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, poda de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Huancarqui: Pampa Blanca, Tomaca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:08</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6048&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>e7040204decb1793a8b51baaca7d158cea9dfedbd220d75d4e17da6a60d9fec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6046</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Ciudad Municipal Sector 3-4-5-6-7-8, Granjeros Unidos I, Guardia Republicana del Peru, Victor Raul Haya de La Torre, Villa del Cono Norte, Virgen de Chapi.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (mantenimiento de</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ciudad Municipal desde BC - 200490.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 15 DE SETIEMBRE DE 2026
+Circuito : Ciudad Municipal desde BC - 200490.
+Hora : 07:30 a 13:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (mantenimiento de subestaciones, inserción de nueva subestación).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Ciudad Municipal Sector 3-4-5-6-7-8, Granjeros Unidos I, Guardia Republicana del Peru, Victor Raul Haya de La Torre, Villa del Cono Norte, Virgen de Chapi.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:06</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6046&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>b3847a67103c00e1ef8912143e21095f5cb4229f17ed8ef0e9abaaa6d1dafa39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6049</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tisco, de Tisco</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Tisco: Cotacota, Tisco.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de pararrayos, instalación de aislador.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Callalli 22.9 desde CC - 880015.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7559, 7560, 7561, 7562, 7599.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 15 DE SETIEMBRE DE 2026:
+Circuito : Callalli 22.9 desde CC - 880015.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Cambio de pararrayos, instalación de aislador.
+Zonas afectadas: Urbanizaciones del distrito de Tisco: Cotacota, Tisco.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7559, 7560, 7561, 7562, 7599.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:08</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6049&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2457faa48bb94651c0d026d090fa22e6ca6c55a9e900a713707cf7c0c0d9bfa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6050</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Lomas, de Lomas</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Chala desde REC - 200157.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 17 DE SETIEMBRE DE 2026:
+Circuito : Chala desde REC - 200157.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).
+Zonas afectadas: Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:09</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6050&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>11ed35b23d06fa366106618652c8ba5d79dc4adbc2c6143451229f9c2e3056f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Yura, de Yura</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (levantamiento de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde CC - 080314.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 17 DE SETIEMBRE DE 2026:
+Circuito : P. Yura desde CC - 080314.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (levantamiento de deficiencias).
+Zonas afectadas: Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 14/09/2026 10:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 10:10</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6051&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>3a5222fabac5646c96e8bdb63997d777149243f549815e0dc933d20934ddbe22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -801,7 +1305,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:26:38</t>
+          <t>2026-09-14 16:24:07</t>
         </is>
       </c>
     </row>
@@ -825,7 +1329,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -837,7 +1341,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -849,7 +1353,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -897,7 +1401,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -909,7 +1413,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -921,7 +1425,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -948,7 +1452,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maca, de Maca</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Maca: Maca.</t>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de estructuras de media tensión.</t>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Callalli 22.9 desde CC - 910131.</t>
+          <t>Circuito : Pionero II desde CC - 200462.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,179 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7526, 7543, 7527.</t>
+          <t>8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 13 DE SETIEMBRE DE 2026:
-Circuito : Callalli 22.9 desde CC - 910131.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Cambio de estructuras de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Maca: Maca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7526, 7543, 7527.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/09/2026 15:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026 15:00</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6045&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>14d454a780bb8f5a7932546cbe280cd936bdcfb735648235bdc4ca79b20e0121</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6041</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra, de Cocachacra</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la Línea de Transmisión y el transformador.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI Y [39] COCACHACRA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 13 DE SETIEMBRE DE 2026:
-LÍNEAS : [L-3038B] La Curva – Cocachacra y [L-3038C] Cocachacra - Chucarapi.
-SET : [38] CHUCARAPI Y [39] COCACHACRA.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de la Línea de Transmisión y el transformador.
-Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle, Alamos del Valle, Asentamiento Humano "Nuevo San Isidro", Avis Alto Veracruz, Cocachacra, El Canto, Grupo Camposur S.A.C, Los Rosales, Tupac Amaru, Veracruz Grande, Villa del Valle, Villa Ramon Castilla.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513, 8371, 8208, 8212, 8207, 8236, 8213, 8214, 8209, 8210, 8211, 8237, 8252, 8295, 8352, 8379, 8380, 8393, 8395, 8469, 8498, 8511, 8481, 8581, 8507, 8648, 8665, 8669, 8692, 8695.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 08/09/2026 17:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>08/09/2026 17:06</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6041&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>8a59115d966a29c7c242ba25e1b98b97807733fe07a22f4b8839bfdf73d2c0d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pionero II desde CC - 200462.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 15 DE SETIEMBRE DE 2026:
@@ -821,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:07</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6047&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4802647c0980302585f6b7cb04cdc5fb85c2623530cb3eb2ae7abc5c211dc753</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6048</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Huancarqui, de Huancarqui</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Huancarqui: Pampa Blanca, Tomaca.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, poda de árboles).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde BC - 810113.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 15 DE SETIEMBRE DE 2026:
@@ -905,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:08</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6048&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>e7040204decb1793a8b51baaca7d158cea9dfedbd220d75d4e17da6a60d9fec8</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6046</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Ciudad Municipal Sector 3-4-5-6-7-8, Granjeros Unidos I, Guardia Republicana del Peru, Victor Raul Haya de La Torre, Villa del Cono Norte, Virgen de Chapi.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (mantenimiento de</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde BC - 200490.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 15 DE SETIEMBRE DE 2026
@@ -989,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:06</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6046&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>b3847a67103c00e1ef8912143e21095f5cb4229f17ed8ef0e9abaaa6d1dafa39</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6049</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Tisco, de Tisco</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Tisco: Cotacota, Tisco.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de pararrayos, instalación de aislador.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC - 880015.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7559, 7560, 7561, 7562, 7599.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 15 DE SETIEMBRE DE 2026:
@@ -1073,80 +904,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7559, 7560, 7561, 7562, 7599.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:08</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6049&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>2457faa48bb94651c0d026d090fa22e6ca6c55a9e900a713707cf7c0c0d9bfa7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6050</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Lomas, de Lomas</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde REC - 200157.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 17 DE SETIEMBRE DE 2026:
@@ -1157,80 +988,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:09</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6050&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>11ed35b23d06fa366106618652c8ba5d79dc4adbc2c6143451229f9c2e3056f5</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6051</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (levantamiento de deficiencias).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde CC - 080314.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 17 DE SETIEMBRE DE 2026:
@@ -1241,30 +1072,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:10</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6051&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>3a5222fabac5646c96e8bdb63997d777149243f549815e0dc933d20934ddbe22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1305,7 +1136,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14 16:24:07</t>
+          <t>2026-09-15 15:03:24</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1160,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1172,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1184,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1256,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1283,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 15:03:24</t>
+          <t>2026-09-16 15:00:06</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
+  <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Lomas, de Lomas</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.</t>
+          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).</t>
+          <t>Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pionero II desde CC - 200462.</t>
+          <t>Circuito : Chala desde REC - 200157.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,346 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
+          <t>9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 15 DE SETIEMBRE DE 2026:
-Circuito : Pionero II desde CC - 200462.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo G.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8766, 8767, 8768, 8769, 8770, 8763, 8764, 8765.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 14/09/2026 10:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 10:07</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6047&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>4802647c0980302585f6b7cb04cdc5fb85c2623530cb3eb2ae7abc5c211dc753</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Huancarqui, de Huancarqui</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Huancarqui: Pampa Blanca, Tomaca.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, poda de árboles).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde BC - 810113.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 15 DE SETIEMBRE DE 2026:
-Circuito : Corire desde BC - 810113.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de postes, poda de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Huancarqui: Pampa Blanca, Tomaca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7133, 7076, 7077, 7080, 7079, 7078, 7357, 7075.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 10:08</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6048&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>e7040204decb1793a8b51baaca7d158cea9dfedbd220d75d4e17da6a60d9fec8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6046</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Ciudad Municipal Sector 3-4-5-6-7-8, Granjeros Unidos I, Guardia Republicana del Peru, Victor Raul Haya de La Torre, Villa del Cono Norte, Virgen de Chapi.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (mantenimiento de</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ciudad Municipal desde BC - 200490.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 15 DE SETIEMBRE DE 2026
-Circuito : Ciudad Municipal desde BC - 200490.
-Hora : 07:30 a 13:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (mantenimiento de subestaciones, inserción de nueva subestación).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Ciudad Municipal Sector 3-4-5-6-7-8, Granjeros Unidos I, Guardia Republicana del Peru, Victor Raul Haya de La Torre, Villa del Cono Norte, Virgen de Chapi.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3850, 3605, 2628, 1746, 2971, 3536, 3535, 3534, 3533, 1930, 3683, 5055, 1744, 3604, 4453, 1745, 5921, 10114, 10328.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 14/09/2026 10:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 10:06</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6046&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>b3847a67103c00e1ef8912143e21095f5cb4229f17ed8ef0e9abaaa6d1dafa39</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6049</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Tisco, de Tisco</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Tisco: Cotacota, Tisco.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de pararrayos, instalación de aislador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Callalli 22.9 desde CC - 880015.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7559, 7560, 7561, 7562, 7599.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 15 DE SETIEMBRE DE 2026:
-Circuito : Callalli 22.9 desde CC - 880015.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Cambio de pararrayos, instalación de aislador.
-Zonas afectadas: Urbanizaciones del distrito de Tisco: Cotacota, Tisco.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7559, 7560, 7561, 7562, 7599.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 14/09/2026 10:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 10:08</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6049&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2457faa48bb94651c0d026d090fa22e6ca6c55a9e900a713707cf7c0c0d9bfa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Lomas, de Lomas</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Chala desde REC - 200157.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 17 DE SETIEMBRE DE 2026:
@@ -988,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:09</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6050&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>11ed35b23d06fa366106618652c8ba5d79dc4adbc2c6143451229f9c2e3056f5</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6051</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (levantamiento de deficiencias).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde CC - 080314.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 17 DE SETIEMBRE DE 2026:
@@ -1072,30 +736,115 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 14/09/2026 10:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>14/09/2026 10:10</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6051&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>3a5222fabac5646c96e8bdb63997d777149243f549815e0dc933d20934ddbe22</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS SET : [9] SAN LUIS.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 20 DE SETIEMBRE DE 2026:
+LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS
+SET : [9] SAN LUIS.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.
+Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 16/09/2026 17:55 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:55</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6052&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5db27a96c4ee625f45baa56eebe47cf023d4b8f4ceb1451c9effec9c56b60757</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1136,7 +885,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:06</t>
+          <t>2026-09-17 15:03:57</t>
         </is>
       </c>
     </row>
@@ -1160,7 +909,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1172,7 +921,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1184,7 +933,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1232,7 +981,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1244,7 +993,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1005,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1032,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:03:57</t>
+          <t>2026-09-18 14:32:44</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
-  <autoFilter ref="A1:P4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
+  <autoFilter ref="A1:P13"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lomas, de Lomas</t>
+          <t>Mollendo, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
+          <t>Urbanizaciones del distrito de Mollendo: Cercado de Mollendo, Inclan, Los Delfines de Mollendo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).</t>
+          <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Chala desde REC - 200157.</t>
+          <t>Circuito : [3101] CERCADO.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,81 +638,81 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
+          <t>8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8006, 8032, 8011, 8022, 8027, 8002, 8034, 8005, 8368, 8369, 8420, 8437, 8487, 8488, 8566, 8501, 8576, 8603, 8640, 8029, 8408, 8428.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-JUEVES, 17 DE SETIEMBRE DE 2026:
-Circuito : Chala desde REC - 200157.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de las redes de media tensión (limpieza y cambio de aisladores, cambio de seccionadores).
-Zonas afectadas: Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9682, 9827, 9349, 9847.</t>
+DOMINGO, 20 DE SETIEMBRE DE 2026:
+Circuito : [3101] CERCADO.
+Hora : 07:00 a 15:30 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Cercado de Mollendo, Inclan, Los Delfines de Mollendo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8006, 8032, 8011, 8022, 8027, 8002, 8034, 8005, 8368, 8369, 8420, 8437, 8487, 8488, 8566, 8501, 8576, 8603, 8640, 8029, 8408, 8428.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>el 14/09/2026 10:09 por Cuenta del sistema</t>
+          <t>el 18/09/2026 15:27 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 10:09</t>
+          <t>18/09/2026 15:27</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6050&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6054&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>11ed35b23d06fa366106618652c8ba5d79dc4adbc2c6143451229f9c2e3056f5</t>
+          <t>22011f338cd68cacbfd1da387b23211cdbd3c754a60cefe99b4ea765e9340d6c</t>
         </is>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Yura, de Yura</t>
+          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.</t>
+          <t>Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (levantamiento de deficiencias).</t>
+          <t>Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Circuito : P. Yura desde CC - 080314.</t>
+          <t>LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS SET : [9] SAN LUIS.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -722,94 +722,10 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
+          <t>3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 17 DE SETIEMBRE DE 2026:
-Circuito : P. Yura desde CC - 080314.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (levantamiento de deficiencias).
-Zonas afectadas: Urbanizaciones de distrito de Yura: Ciudad Municipal Zona 9, El Chaparal, San Geronimo Etapa 1, Villa Los Milagros, Villa Los Milagros II Etapa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4091, 4177, 4452, 5047, 5048, 10157, 5597, 5598, 5627, 5172P, 5765, 5382, 5899, 4567.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 14/09/2026 10:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 10:10</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6051&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>3a5222fabac5646c96e8bdb63997d777149243f549815e0dc933d20934ddbe22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS SET : [9] SAN LUIS.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 20 DE SETIEMBRE DE 2026:
@@ -821,30 +737,835 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 16/09/2026 17:55 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:55</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6052&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>5db27a96c4ee625f45baa56eebe47cf023d4b8f4ceb1451c9effec9c56b60757</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6053</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [9301] SAN ANTONIO.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7603, 7611, 7608, 7609, 7604, 7610, 7605, 7602, 7606, 7607.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 20 DE SETIEMBRE DE 2026:
+Circuito : [9301] SAN ANTONIO.
+Hora : 12:00 a 13:00 Hrs.
+Motivo : Mantenimiento del transformador de la subestación de Caylloma.
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7605, 7602, 7606, 7607.</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>el 16/09/2026 17:55 por Cuenta del sistema</t>
+          <t>el 18/09/2026 15:26 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026 17:55</t>
+          <t>18/09/2026 15:26</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6052&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6053&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5db27a96c4ee625f45baa56eebe47cf023d4b8f4ceb1451c9effec9c56b60757</t>
+          <t>c867b7a6b7f7303164b561149d9bf89d402f7627d52a101b0cdd58e798c9a6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6056</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de distribución.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3783.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 21 DE SETIEMBRE DE 2026.
+Circuito : SED 3783.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador de distribución.
+Zonas afectadas: Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:38</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6056&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>b57477e70c6da80c0d8f2567fdd10d0ad4741f9dfa55a3cf6aa71256950e2242</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6057</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de distribución.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2869.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 21 DE SETIEMBRE DE 2026.
+Circuito : SED 2869.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador de distribución.
+Zonas afectadas: Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:39 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:39</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6057&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>5c7147112009db8f4939788f36870338838aadd2ce358b066ffbd18e808fe162</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6058</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de tablero.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3420.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 22 DE SETIEMBRE DE 2026.
+Circuito : SED 3420.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de tablero.
+Zonas afectadas: Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:40</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6058&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>fdf1d84a4817aee731bd3098f08a23a145c8af3883c2b668faa591dd63c06aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de tablero.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5873.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 22 DE SETIEMBRE DE 2026.
+Circuito : SED 5873.
+Hora : 21:00 a 23:59 Hrs.
+Motivo : Cambio de tablero.
+Zonas afectadas: Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:40</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6059&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>68c8ecde350807825bbd85afffa9f679c7e6bc0a667344c0657f044290bbb22a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Huancarqui, de Huancarqui</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde CC - 810130.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 24 DE SETIEMBRE DE 2026:
+Circuito : Corire desde CC - 810130.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)
+Zonas afectadas: Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:43 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6063&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>81f596b3ff77db6cf863896bbb013df7f4a986076a1eabd22794d5e49961f53d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6060</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de tablero.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4495.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 24 DE SETIEMBRE DE 2026.
+Circuito : SED 4495.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de tablero.
+Zonas afectadas: Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:41 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:41</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6060&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>04be2dd6380b40fce549211376407ee6565f541be704bafa08fa5bff4b9fc8bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6061</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4696.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 24 DE SETIEMBRE DE 2026.
+Circuito : SED 4696.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Mantenimiento de subestación.
+Zonas afectadas: Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:42</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6061&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>ac0bb57cbf179804f41eccb979ad79d1a1e0736d1352e12c5210fe2b4040f5b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Montaje de nueva subestación de distribución.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Las Flores desde EMT – 20428</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5618, 4601, 5085.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 25 DE SETIEMBRE DE 2026:
+Circuito : Las Flores desde EMT – 20428
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Montaje de nueva subestación de distribución.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:38</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6062</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Uchumayo, de Uchumayo</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de distribución.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1091</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 25 DE SETIEMBRE DE 2026.
+Circuito : SED 1091.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador de distribución.
+Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:42</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -885,7 +1606,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:44</t>
+          <t>2026-09-19 13:56:25</t>
         </is>
       </c>
     </row>
@@ -909,7 +1630,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -921,7 +1642,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -933,7 +1654,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -981,7 +1702,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -993,7 +1714,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1726,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1753,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 13:56:25</t>
+          <t>2026-09-20 14:15:32</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:32</t>
+          <t>2026-09-21 16:29:35</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
-  <autoFilter ref="A1:P13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
+  <autoFilter ref="A1:P10"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mollendo, de Mollendo</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Mollendo: Cercado de Mollendo, Inclan, Los Delfines de Mollendo.</t>
+          <t>Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
+          <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [3101] CERCADO.</t>
+          <t>Circuito : SED 3783.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,261 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8006, 8032, 8011, 8022, 8027, 8002, 8034, 8005, 8368, 8369, 8420, 8437, 8487, 8488, 8566, 8501, 8576, 8603, 8640, 8029, 8408, 8428.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 20 DE SETIEMBRE DE 2026:
-Circuito : [3101] CERCADO.
-Hora : 07:00 a 15:30 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Cercado de Mollendo, Inclan, Los Delfines de Mollendo.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8006, 8032, 8011, 8022, 8027, 8002, 8034, 8005, 8368, 8369, 8420, 8437, 8487, 8488, 8566, 8501, 8576, 8603, 8640, 8029, 8408, 8428.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 15:27 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 15:27</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6054&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>22011f338cd68cacbfd1da387b23211cdbd3c754a60cefe99b4ea765e9340d6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS SET : [9] SAN LUIS.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 20 DE SETIEMBRE DE 2026:
-LÍNEAS : [L-3100] CHILINA - JESUS, [L-3101] CHILINA – SAN LUIS, [L-3102] SAN LUIS-JESUS
-SET : [9] SAN LUIS.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento preventivo de línea de transmisión y pruebas en el transformador.
-Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Alto Selva Alegre Zona A-B-C, Apurímac, Asociación de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliación Zona A y B, El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Gráficos Zona B, Huarangal, Independencia Zona A-B, Javier Heraud, Lealtad Democrática, Leones del Misti, Los Ángeles del Misti, Prog Municipal de Pequeña Industria, San Luis, Tres Balcones del Misti, Villa Asunción, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo, Villa Union, Villa Vitarte, Virgen de Chapi, Urbanizaciones del distrito de Mariano Melgar: A. H. Berlín II, A.H. Berlín, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: Alto Juan XXIII, Alto Misti, Buen Amanecer, C. Granja Viv. San Lazaro Zona A, Edificadores Misti, El Porvenir, El Salvador, Francisco Paulet Mostajo, Héroes del Pacifico, Juan XXIII Zona A-B, La Galaxia, La Galaxia III, Los Girasoles II, Los Girasoles Zona B, Los Incas, Los Jardines de Selva Alegre, Mateo Pumacahua, Nuevo Amanecer, Parque Artesanal, Prolongación Goyeneche, San Francisco de Asis, Sto Blanco, Tomasa Tito Condemayta, Villa Arica, Villa Coyllorite.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3032, 3976, 3653, 3654, 3655, 2406, 3896, 3039, 1676, 3145, 3044, 1368, 3769, 3765, 3766, 3764, 3763, 3767, 3758, 1575, 1848, 1200, 1869, 2501, 3147, 3036, 3038, 1150, 3042, 3040, 3037, 1384, 3329, 1182, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 2587, 3466, 3465, 3449, 3328, 3330, 3473, 3474, 3548, 3547, 3560, 3558, 3557, 3559, 3556, 3354, 3375, 3376, 3643, 3034, 3043, 2724, 3045, 3046, 2045, 3768, 2046, 2742, 3140, 1580, 1543, 3141, 3630, 3686, 2293, 1518, 1866, 3332, 3144, 3419, 3520, 1155, 1151, 3146, 3041, 3033, 3031, 2290, 3786, 1149, 2407, 2588, 4000, 4050, 4102, 4103, 4104, 4105, 4139, 4220, 4218, 4301, 4354, 4355, 4459, 4413, 4414, 4504, 4505, 4530, 4533, 4566, 4643, 4644, 4840, 4771, 4770, 4772, 4774, 4937, 4976, 4918, 5092, 5091, 5051, 5173, 5371, 5428, 5525, 5526, 5549, 5550, 5464, 5650, 5651, 5657, 5688, 5679, 5767, 5811, 5942, 10125, 10020, 10021, 10210, 3846, 3035, 3566, 3642, 3641, 4049, 10340.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/09/2026 17:55 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/09/2026 17:55</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6052&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>5db27a96c4ee625f45baa56eebe47cf023d4b8f4ceb1451c9effec9c56b60757</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6053</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [9301] SAN ANTONIO.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7603, 7611, 7608, 7609, 7604, 7610, 7605, 7602, 7606, 7607.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 20 DE SETIEMBRE DE 2026:
-Circuito : [9301] SAN ANTONIO.
-Hora : 12:00 a 13:00 Hrs.
-Motivo : Mantenimiento del transformador de la subestación de Caylloma.
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7605, 7602, 7606, 7607.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 15:26 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 15:26</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6053&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>c867b7a6b7f7303164b561149d9bf89d402f7627d52a101b0cdd58e798c9a6fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6056</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de distribución.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3783.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 LUNES, 21 DE SETIEMBRE DE 2026.
@@ -900,76 +647,76 @@
 Zonas afectadas: Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:38</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6056&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>b57477e70c6da80c0d8f2567fdd10d0ad4741f9dfa55a3cf6aa71256950e2242</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6057</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2869.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 LUNES, 21 DE SETIEMBRE DE 2026.
@@ -979,76 +726,76 @@
 Zonas afectadas: Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:39</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6057&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>5c7147112009db8f4939788f36870338838aadd2ce358b066ffbd18e808fe162</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6058</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3420.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 22 DE SETIEMBRE DE 2026.
@@ -1058,76 +805,76 @@
 Zonas afectadas: Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:40</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6058&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>fdf1d84a4817aee731bd3098f08a23a145c8af3883c2b668faa591dd63c06aec</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6059</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5873.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 22 DE SETIEMBRE DE 2026.
@@ -1137,80 +884,80 @@
 Zonas afectadas: Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:40</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6059&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>68c8ecde350807825bbd85afffa9f679c7e6bc0a667344c0657f044290bbb22a</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6063</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Huancarqui, de Huancarqui</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810130.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026:
@@ -1221,76 +968,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:43 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:43</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6063&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>81f596b3ff77db6cf863896bbb013df7f4a986076a1eabd22794d5e49961f53d</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6060</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4495.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -1300,76 +1047,76 @@
 Zonas afectadas: Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:41</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6060&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>04be2dd6380b40fce549211376407ee6565f541be704bafa08fa5bff4b9fc8bf</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6061</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4696.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -1379,80 +1126,80 @@
 Zonas afectadas: Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6061&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ac0bb57cbf179804f41eccb979ad79d1a1e0736d1352e12c5210fe2b4040f5b7</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6055</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Montaje de nueva subestación de distribución.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Flores desde EMT – 20428</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026:
@@ -1463,76 +1210,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:38</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6062</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Uchumayo, de Uchumayo</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1091</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1542,30 +1289,30 @@
 Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1606,7 +1353,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:29:35</t>
+          <t>2026-09-22 14:58:57</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1377,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1389,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1401,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1473,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1500,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, de Cayma</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
+          <t>Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador de distribución.</t>
+          <t>Cambio de tablero.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 3783.</t>
+          <t>Circuito : SED 3420.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,164 +638,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 21 DE SETIEMBRE DE 2026.
-Circuito : SED 3783.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador de distribución.
-Zonas afectadas: Zona A de Urb. Villa Cerrillos (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:38</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6056&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>b57477e70c6da80c0d8f2567fdd10d0ad4741f9dfa55a3cf6aa71256950e2242</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6057</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de distribución.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2869.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 21 DE SETIEMBRE DE 2026.
-Circuito : SED 2869.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador de distribución.
-Zonas afectadas: Mz. J-K-L de Urb. Asociación Guillermo Mercado (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:39 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:39</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6057&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>5c7147112009db8f4939788f36870338838aadd2ce358b066ffbd18e808fe162</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de tablero.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3420.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 22 DE SETIEMBRE DE 2026.
@@ -805,76 +647,76 @@
 Zonas afectadas: Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:40</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6058&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>fdf1d84a4817aee731bd3098f08a23a145c8af3883c2b668faa591dd63c06aec</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6059</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5873.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 22 DE SETIEMBRE DE 2026.
@@ -884,80 +726,80 @@
 Zonas afectadas: Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:40</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6059&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>68c8ecde350807825bbd85afffa9f679c7e6bc0a667344c0657f044290bbb22a</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6063</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Huancarqui, de Huancarqui</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810130.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026:
@@ -968,76 +810,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:43 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:43</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6063&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>81f596b3ff77db6cf863896bbb013df7f4a986076a1eabd22794d5e49961f53d</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6060</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4495.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -1047,76 +889,76 @@
 Zonas afectadas: Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:41</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6060&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>04be2dd6380b40fce549211376407ee6565f541be704bafa08fa5bff4b9fc8bf</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6061</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4696.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -1126,80 +968,80 @@
 Zonas afectadas: Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6061&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>ac0bb57cbf179804f41eccb979ad79d1a1e0736d1352e12c5210fe2b4040f5b7</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6055</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Montaje de nueva subestación de distribución.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Flores desde EMT – 20428</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026:
@@ -1210,76 +1052,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:38</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6062</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Uchumayo, de Uchumayo</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1091</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1289,25 +1131,183 @@
 Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 17:42</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5018.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 25 DE SETIEMBRE DE 2026.
+Circuito : SED 5018.
+Hora : 08:30 a 08:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 7:56</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6064&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>6d2cc873781f168d4bcdcf5ad0642d1192d3d14c6235f1a0d10cc9db4d62f15d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6065</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4681.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 25 DE SETIEMBRE DE 2026.
+Circuito : SED 4681.
+Hora : 09:00 a 09:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
+          <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026 17:42</t>
+          <t>23/09/2026 7:56</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6065&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
+          <t>95fe43aa219630c6f1ba3a7766ee0b5d898584ea2cb17a3e520ed1c898e486cc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 14:58:57</t>
+          <t>2026-09-23 15:03:56</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
-  <autoFilter ref="A1:P10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Huancarqui, de Huancarqui</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
+          <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de tablero.</t>
+          <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 3420.</t>
+          <t>Circuito : Corire desde CC - 810130.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,170 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 22 DE SETIEMBRE DE 2026.
-Circuito : SED 3420.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de tablero.
-Zonas afectadas: Mz. 3-10 de Zona B de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:40</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6058&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>fdf1d84a4817aee731bd3098f08a23a145c8af3883c2b668faa591dd63c06aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6059</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>23:55</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de tablero.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5873.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 22 DE SETIEMBRE DE 2026.
-Circuito : SED 5873.
-Hora : 21:00 a 23:59 Hrs.
-Motivo : Cambio de tablero.
-Zonas afectadas: Cuadra 4 de Calle Nicolas de Pierola, Cuadra 2 de Calle Alto la Luna (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:40 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:40</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6059&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>68c8ecde350807825bbd85afffa9f679c7e6bc0a667344c0657f044290bbb22a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Huancarqui, de Huancarqui</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde CC - 810130.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026:
@@ -810,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:43 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:43</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6063&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>81f596b3ff77db6cf863896bbb013df7f4a986076a1eabd22794d5e49961f53d</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6060</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4495.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -889,76 +731,76 @@
 Zonas afectadas: Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:41</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6060&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>04be2dd6380b40fce549211376407ee6565f541be704bafa08fa5bff4b9fc8bf</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6061</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4696.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 24 DE SETIEMBRE DE 2026.
@@ -968,80 +810,80 @@
 Zonas afectadas: Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6061&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ac0bb57cbf179804f41eccb979ad79d1a1e0736d1352e12c5210fe2b4040f5b7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6055</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Montaje de nueva subestación de distribución.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Flores desde EMT – 20428</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026:
@@ -1052,76 +894,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:38</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6062</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Uchumayo, de Uchumayo</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1091</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1131,76 +973,76 @@
 Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6064</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5018.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1210,76 +1052,76 @@
 Zonas afectadas: Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23/09/2026 7:56</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6064&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>6d2cc873781f168d4bcdcf5ad0642d1192d3d14c6235f1a0d10cc9db4d62f15d</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6065</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4681.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1289,30 +1131,30 @@
 Zonas afectadas: Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23/09/2026 7:56</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6065&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>95fe43aa219630c6f1ba3a7766ee0b5d898584ea2cb17a3e520ed1c898e486cc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1353,7 +1195,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:03:56</t>
+          <t>2026-09-24 15:10:46</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1219,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1231,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1243,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1315,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1342,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
+  <autoFilter ref="A1:P10"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1153,8 +1153,176 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6067</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, Yanahuara, de Cayma, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [301] YANAHUARA III.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 27 DE SETIEMBRE DE 2026:
+Circuito : [301] YANAHUARA III.
+Hora : 06:00 a 13:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).
+Zonas afectadas: Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 8:03 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 8:03</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6067&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9cbcc97f9e7c0bfc823b2c942cae7d2f55cdac0a71e295173b2cb18ad886ece1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6066</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Mejía, Mollendo, de Mejía, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [3601] MEJIA.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 27 DE SETIEMBRE DE 2026:
+Circuito : [3601] MEJIA.
+Hora : 07:30 a 16:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)
+Zonas afectadas: Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6066&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>d8f8b1256b382cf3c36385a98dd929a6696e8230b4191c6b83942cc4df5714f8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1195,7 +1363,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:10:46</t>
+          <t>2026-09-25 15:18:40</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1387,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1399,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1411,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1459,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1471,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1483,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1510,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
-  <autoFilter ref="A1:P10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
+  <autoFilter ref="A1:P13"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Huancarqui, de Huancarqui</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)</t>
+          <t>Montaje de nueva subestación de distribución.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Corire desde CC - 810130.</t>
+          <t>Circuito : Las Flores desde EMT – 20428</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,252 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
+          <t>5618, 4601, 5085.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 24 DE SETIEMBRE DE 2026:
-Circuito : Corire desde CC - 810130.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión (cambio de crucetas, limpieza de aisladores, podado de árboles)
-Zonas afectadas: Urbanizaciones del distrito de Huancarqui: 23 de junio, Huancarqui, La Laja, Las Islas, Nueva Esperanza, Sector Las Tiendas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7159, 7050, 7049, 7047, 7045, 8541, 7046, 7158, 7048, 7168, 7169, 7959.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:43 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:43</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6063&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>81f596b3ff77db6cf863896bbb013df7f4a986076a1eabd22794d5e49961f53d</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de tablero.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4495.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 24 DE SETIEMBRE DE 2026.
-Circuito : SED 4495.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de tablero.
-Zonas afectadas: Mz. C-D-E-G de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:41 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:41</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6060&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>04be2dd6380b40fce549211376407ee6565f541be704bafa08fa5bff4b9fc8bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4696.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 24 DE SETIEMBRE DE 2026.
-Circuito : SED 4696.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Mantenimiento de subestación.
-Zonas afectadas: Mz. R de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:42</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6061&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>ac0bb57cbf179804f41eccb979ad79d1a1e0736d1352e12c5210fe2b4040f5b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6055</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Montaje de nueva subestación de distribución.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Las Flores desde EMT – 20428</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5618, 4601, 5085.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026:
@@ -894,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:38</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6062</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Uchumayo, de Uchumayo</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1091</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -973,76 +731,76 @@
 Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>18/09/2026 17:42</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6064</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5018.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1052,76 +810,76 @@
 Zonas afectadas: Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23/09/2026 7:56</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6064&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>6d2cc873781f168d4bcdcf5ad0642d1192d3d14c6235f1a0d10cc9db4d62f15d</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6065</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4681.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 25 DE SETIEMBRE DE 2026.
@@ -1131,80 +889,80 @@
 Zonas afectadas: Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23/09/2026 7:56</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6065&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>95fe43aa219630c6f1ba3a7766ee0b5d898584ea2cb17a3e520ed1c898e486cc</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6067</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>27/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cayma, Yanahuara, de Cayma, de Yanahuara</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : [301] YANAHUARA III.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 27 DE SETIEMBRE DE 2026:
@@ -1215,80 +973,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 8:03</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6067&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>9cbcc97f9e7c0bfc823b2c942cae7d2f55cdac0a71e295173b2cb18ad886ece1</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6066</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>27/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Mejía, Mollendo, de Mejía, de Mollendo</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3601] MEJIA.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 27 DE SETIEMBRE DE 2026:
@@ -1299,30 +1057,514 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6066&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>d8f8b1256b382cf3c36385a98dd929a6696e8230b4191c6b83942cc4df5714f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Uraca, de Uraca</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Uraca: La Barrera, Uraca.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde CC - 810114.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7085, 7086, 7495.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 29 DE SETIEMBRE DE 2026:
+Circuito : Corire desde CC - 810114.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Uraca: La Barrera, Uraca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7085, 7086, 7495.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 19:17 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 19:17</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6068&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>445933f04543e2674b8c82d925408562a35d4fae1c4df0d78f4929d1827a1a0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4377.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 29 DE SETIEMBRE DE 2026.
+Circuito : SED 4377.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Mantenimiento de subestación.
+Zonas afectadas: Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 19:19</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6070&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>05fca199e4747811d52cf5d909b6b2647f3b50dbd6f887f383cdfd6215544ce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4295.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 29 DE SETIEMBRE DE 2026.
+Circuito : SED 4295.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Mantenimiento de subestación.
+Zonas afectadas: Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>el 25/09/2026 8:02 por Cuenta del sistema</t>
+          <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026 8:02</t>
+          <t>25/09/2026 19:19</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6066&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6071&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>d8f8b1256b382cf3c36385a98dd929a6696e8230b4191c6b83942cc4df5714f8</t>
+          <t>facd191b0b4c67377f88bd573c3c4af279b5fa89ff56c7eb782c95e2ec3bfae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de terminaciones de cable subterráneo.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 10263.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
+Circuito : SED 10263.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de terminaciones de cable subterráneo.
+Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 19:20</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6072&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>7d40f159b4d5cdf5d1d68e35a5c5a8c99fb2d26158c7456ce9f38d9e2f96c327</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de terminaciones de cable subterráneo.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5373.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
+Circuito : SED 5373.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de terminaciones de cable subterráneo.
+Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 19:20</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6073&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>648ef5a1b262ced823ce4b4119095faf566a7070a18c121061e9e2c30df88afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6069</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Cocachacra, de Cocachacra</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes eléctricas de media tensión.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : El Fiscal desde REC - 200543.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 30 DE SETIEMBRE DE 2026:
+Circuito : El Fiscal desde REC - 200543.
+Hora : 08:30 a 16:30 Hrs.
+Motivo : Mantenimiento de redes eléctricas de media tensión.
+Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 25/09/2026 19:18 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 19:18</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6069&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2d933c84750b7f202beb0ce4bd56d6030e66a68b8067317cac7f9645c26742f7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1363,7 +1605,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:18:40</t>
+          <t>2026-09-26 14:32:15</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1629,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1641,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1653,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1701,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1713,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1725,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1752,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P13" headerRowCount="1">
-  <autoFilter ref="A1:P13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Cayma, Yanahuara, de Cayma, de Yanahuara</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.</t>
+          <t>Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Montaje de nueva subestación de distribución.</t>
+          <t>Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Las Flores desde EMT – 20428</t>
+          <t>Circuito : [301] YANAHUARA III.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,331 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>5618, 4601, 5085.</t>
+          <t>1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 25 DE SETIEMBRE DE 2026:
-Circuito : Las Flores desde EMT – 20428
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Montaje de nueva subestación de distribución.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Asoc. Los Montoneros, Asoc. Agroindustrial Fortaleza.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5618, 4601, 5085.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:38 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:38</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6055&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>5480854177b982081487a68d289035042dceafa9d5a5d23e379295047d2587ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6062</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Uchumayo, de Uchumayo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Lateral 4 el Cural (Distrito de Uchumayo).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de distribución.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1091</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 25 DE SETIEMBRE DE 2026.
-Circuito : SED 1091.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador de distribución.
-Zonas afectadas: Lateral 4 el Cural (Distrito de Uchumayo).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 18/09/2026 17:42 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>18/09/2026 17:42</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6062&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>b62f5976baa44fb371165d776ab880d9ac1617ec26642fdcd10e6e17b8a29f03</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5018.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 25 DE SETIEMBRE DE 2026.
-Circuito : SED 5018.
-Hora : 08:30 a 08:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. A-B de Urb. Emperatriz (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23/09/2026 7:56</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6064&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6d2cc873781f168d4bcdcf5ad0642d1192d3d14c6235f1a0d10cc9db4d62f15d</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6065</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4681.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 25 DE SETIEMBRE DE 2026.
-Circuito : SED 4681.
-Hora : 09:00 a 09:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. A de Urb. La Chacrita, MZ. F-G de Urb. Bella Horizonte, Mz. D de Urb. La Marina (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 23/09/2026 7:56 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23/09/2026 7:56</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6065&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95fe43aa219630c6f1ba3a7766ee0b5d898584ea2cb17a3e520ed1c898e486cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6067</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>27/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, Yanahuara, de Cayma, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [301] YANAHUARA III.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 27 DE SETIEMBRE DE 2026:
@@ -973,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 8:03</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6067&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>9cbcc97f9e7c0bfc823b2c942cae7d2f55cdac0a71e295173b2cb18ad886ece1</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6066</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>27/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mejía, Mollendo, de Mejía, de Mollendo</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3601] MEJIA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 27 DE SETIEMBRE DE 2026:
@@ -1057,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 8:02</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6066&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>d8f8b1256b382cf3c36385a98dd929a6696e8230b4191c6b83942cc4df5714f8</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6068</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Uraca, de Uraca</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Uraca: La Barrera, Uraca.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810114.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7085, 7086, 7495.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026:
@@ -1141,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7085, 7086, 7495.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:17</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6068&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>445933f04543e2674b8c82d925408562a35d4fae1c4df0d78f4929d1827a1a0b</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6070</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4377.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026.
@@ -1220,76 +899,76 @@
 Zonas afectadas: Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:19</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6070&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>05fca199e4747811d52cf5d909b6b2647f3b50dbd6f887f383cdfd6215544ce9</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6071</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4295.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026.
@@ -1299,76 +978,76 @@
 Zonas afectadas: Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:19</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6071&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>facd191b0b4c67377f88bd573c3c4af279b5fa89ff56c7eb782c95e2ec3bfae8</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6072</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10263.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -1378,76 +1057,76 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6072&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>7d40f159b4d5cdf5d1d68e35a5c5a8c99fb2d26158c7456ce9f38d9e2f96c327</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6073</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5373.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -1457,80 +1136,80 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6073&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>648ef5a1b262ced823ce4b4119095faf566a7070a18c121061e9e2c30df88afe</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6069</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes eléctricas de media tensión.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : El Fiscal desde REC - 200543.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026:
@@ -1541,30 +1220,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:18</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6069&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>2d933c84750b7f202beb0ce4bd56d6030e66a68b8067317cac7f9645c26742f7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1605,7 +1284,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:32:15</t>
+          <t>2026-09-27 15:11:04</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1308,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1320,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1332,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1404,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1431,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:11:04</t>
+          <t>2026-09-28 18:10:57</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, Yanahuara, de Cayma, de Yanahuara</t>
+          <t>Uraca, de Uraca</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.</t>
+          <t>Urbanizaciones del distrito de Uraca: La Barrera, Uraca.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).</t>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [301] YANAHUARA III.</t>
+          <t>Circuito : Corire desde CC - 810114.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,178 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
+          <t>7085, 7086, 7495.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 27 DE SETIEMBRE DE 2026:
-Circuito : [301] YANAHUARA III.
-Hora : 06:00 a 13:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de poste, reubicación de subestación).
-Zonas afectadas: Urbanizaciones del distrito de Cayma: Alto Gloria, El Rosario, Heresi, La Candelaria, La Valencia, Los Sauces, Quinta Gamero, Señorial. Urbanizaciones del distrito de Yanahuara: Buganvilas, El Rosario, Las Retamas, Los Claveles, Tronco de Oro, Yanahuara.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1542, 4011, 2104, 3165, 2680, 3634, 2500, 3274, 1784, 1439, 3260, 3261, 3263, 3264, 2550, 3259, 3257, 3258, 1450, 3082, 3081, 3083, 3084, 3267, 3667, 3580, 2757, 1800, 2584, 2360, 1270, 1211, 3167, 2327, 3270, 1811, 3166, 1731, 1233, 3963, 4324, 4361, 4390, 4450, 4664, 4654, 4721, 4732, 4882, 4808, 4818, 5022, 5060, 5179, 5017, 5328, 4970, 5056, 5387, 3164, 1232, 10079, 10260, 10261, 10295, 4916, 3958, 5945.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6067&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>9cbcc97f9e7c0bfc823b2c942cae7d2f55cdac0a71e295173b2cb18ad886ece1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>27/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mejía, Mollendo, de Mejía, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [3601] MEJIA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 27 DE SETIEMBRE DE 2026:
-Circuito : [3601] MEJIA.
-Hora : 07:30 a 16:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de postes, cambio de conductor)
-Zonas afectadas: Urbanizaciones del distrito de Mejía: Almar, Costa Morena, Guilardi, J.C. Mariategui, La Perla de Mejia, Las Casuarinas, Las Casuarinas II, Las Gaviotas, Las Palmeras, Los Lotos Gilardi, San Jose, Santa Elena. Urbanizaciones del distrito de Mollendo: Arizona, Costa Palmeras.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8155, 8102, 8636, 8110, 8248, 8098, 8099, 8100, 8101, 8103, 8160, 8159, 8158, 8157, 8131, 8149, 8150, 8151, 8152, 8244, 8147, 8105, 8104, 8106, 8107, 8108, 8261, 8265, 8133, 8270, 8154, 8293, 8230, 8229, 8135, 8245, 8134, 8136, 8140, 8142, 8143, 8153, 8139, 8156, 8302, 8345, 8351, 8366, 8367, 8388, 8392, 8400, 8399, 8401, 8402, 8397, 8398, 8424, 8425, 8426, 8429, 8442, 8456, 8457, 8464, 8474, 8473, 8468, 8491, 8495, 8419, 8497, 8502, 8535, 8467, 8466, 8558, 8574, 8587, 8637, 8109, 8654, 8728, 10059, 8510, 8729, 8350, 8235, 10297, 8146, 8138, 8137, 8132, 8297, 8335, 8679, 10137.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 8:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 8:02</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6066&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>d8f8b1256b382cf3c36385a98dd929a6696e8230b4191c6b83942cc4df5714f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6068</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Uraca, de Uraca</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Uraca: La Barrera, Uraca.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde CC - 810114.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7085, 7086, 7495.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026:
@@ -820,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7085, 7086, 7495.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:17</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6068&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>445933f04543e2674b8c82d925408562a35d4fae1c4df0d78f4929d1827a1a0b</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6070</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4377.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026.
@@ -899,76 +731,76 @@
 Zonas afectadas: Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:19</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6070&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>05fca199e4747811d52cf5d909b6b2647f3b50dbd6f887f383cdfd6215544ce9</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6071</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4295.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 29 DE SETIEMBRE DE 2026.
@@ -978,76 +810,76 @@
 Zonas afectadas: Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:19</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6071&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>facd191b0b4c67377f88bd573c3c4af279b5fa89ff56c7eb782c95e2ec3bfae8</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6072</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10263.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -1057,76 +889,76 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6072&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>7d40f159b4d5cdf5d1d68e35a5c5a8c99fb2d26158c7456ce9f38d9e2f96c327</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6073</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5373.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -1136,80 +968,80 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6073&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>648ef5a1b262ced823ce4b4119095faf566a7070a18c121061e9e2c30df88afe</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6069</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes eléctricas de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : El Fiscal desde REC - 200543.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026:
@@ -1220,30 +1052,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:18</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6069&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2d933c84750b7f202beb0ce4bd56d6030e66a68b8067317cac7f9645c26742f7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1284,7 +1116,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:10:57</t>
+          <t>2026-09-29 16:32:16</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1140,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1152,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1164,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1236,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1263,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 16:32:16</t>
+          <t>2026-09-30 16:25:40</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
+  <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Uraca, de Uraca</t>
+          <t>Miraflores, de Miraflores</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Uraca: La Barrera, Uraca.</t>
+          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).</t>
+          <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Corire desde CC - 810114.</t>
+          <t>Circuito : SED 10263.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,250 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>7085, 7086, 7495.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 29 DE SETIEMBRE DE 2026:
-Circuito : Corire desde CC - 810114.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de aisladores, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Uraca: La Barrera, Uraca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7085, 7086, 7495.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:17 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:17</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6068&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>445933f04543e2674b8c82d925408562a35d4fae1c4df0d78f4929d1827a1a0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4377.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 29 DE SETIEMBRE DE 2026.
-Circuito : SED 4377.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Mantenimiento de subestación.
-Zonas afectadas: Mz. B-C de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:19</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6070&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>05fca199e4747811d52cf5d909b6b2647f3b50dbd6f887f383cdfd6215544ce9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6071</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4295.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 29 DE SETIEMBRE DE 2026.
-Circuito : SED 4295.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Mantenimiento de subestación.
-Zonas afectadas: Mz. A de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:19 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:19</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6071&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>facd191b0b4c67377f88bd573c3c4af279b5fa89ff56c7eb782c95e2ec3bfae8</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de terminaciones de cable subterráneo.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 10263.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -889,76 +647,76 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6072&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>7d40f159b4d5cdf5d1d68e35a5c5a8c99fb2d26158c7456ce9f38d9e2f96c327</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6073</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Miraflores, de Miraflores</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de terminaciones de cable subterráneo.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5373.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
@@ -968,80 +726,80 @@
 Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:20</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6073&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>648ef5a1b262ced823ce4b4119095faf566a7070a18c121061e9e2c30df88afe</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6069</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes eléctricas de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : El Fiscal desde REC - 200543.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 30 DE SETIEMBRE DE 2026:
@@ -1052,30 +810,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 25/09/2026 19:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25/09/2026 19:18</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6069&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2d933c84750b7f202beb0ce4bd56d6030e66a68b8067317cac7f9645c26742f7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1116,7 +874,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 16:25:40</t>
+          <t>2026-10-01 17:02:52</t>
         </is>
       </c>
     </row>
@@ -1140,7 +898,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1152,7 +910,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1164,7 +922,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1236,7 +994,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1021,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,13 +80,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,31 +168,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
-  <autoFilter ref="A1:P4"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Hora inicio"/>
-    <tableColumn id="4" name="Hora fin"/>
-    <tableColumn id="5" name="Distrito"/>
-    <tableColumn id="6" name="Zona afectada"/>
-    <tableColumn id="7" name="Motivo"/>
-    <tableColumn id="8" name="Ubicación"/>
-    <tableColumn id="9" name="Título"/>
-    <tableColumn id="10" name="Subestaciones / SED"/>
-    <tableColumn id="11" name="Descripción completa"/>
-    <tableColumn id="12" name="Categoría"/>
-    <tableColumn id="13" name="Creado"/>
-    <tableColumn id="14" name="Modificado"/>
-    <tableColumn id="15" name="URL"/>
-    <tableColumn id="16" name="Hash"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,254 +562,9 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de terminaciones de cable subterráneo.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 10263.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
-Circuito : SED 10263.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de terminaciones de cable subterráneo.
-Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:20</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6072&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>7d40f159b4d5cdf5d1d68e35a5c5a8c99fb2d26158c7456ce9f38d9e2f96c327</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Miraflores, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de terminaciones de cable subterráneo.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5373.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 30 DE SETIEMBRE DE 2026.
-Circuito : SED 5373.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de terminaciones de cable subterráneo.
-Zonas afectadas: Mz. R4 de Urb. Alameda Salaverry (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:20</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6073&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>648ef5a1b262ced823ce4b4119095faf566a7070a18c121061e9e2c30df88afe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6069</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra, de Cocachacra</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes eléctricas de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : El Fiscal desde REC - 200543.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 30 DE SETIEMBRE DE 2026:
-Circuito : El Fiscal desde REC - 200543.
-Hora : 08:30 a 16:30 Hrs.
-Motivo : Mantenimiento de redes eléctricas de media tensión.
-Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Caraquen, El Toro, La Pascana.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 25/09/2026 19:18 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25/09/2026 19:18</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6069&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2d933c84750b7f202beb0ce4bd56d6030e66a68b8067317cac7f9645c26742f7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -855,173 +582,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:02:52</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:17:26</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>REQUESTS_STATIC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>81</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>81</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>3</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,432 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>6076</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Asentamiento B1, Avg Aspein, Avg Los Olivos, B-3, Corazon de Jesus, E - 8, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A-B-C, Modulo A Sector 5 Modulo C Sector 2, Nuevo Progreso C-2, Rafael Hoyos Rubio.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pionero I desde BC - 950122.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>6194, 6250, 6187, 6197, 8818, 6184, 7665, 6183, 6165, 6164, 8904, 6193, 6192, 6191, 6190, 6203, 6444, 6622, 6188, 6206, 10215, 6205, 6204, 6185, 6199, 6172, 7654, 6171, 6515, 6170, 6169, 6154, 6963, 8886, 8889, 6266, 6280, 6166, 7820, 6625, 6177, 7705, 6432, 6178, 6175, 10251, 6174, 6582, 6163, 7919, 7911, 6162, 6161, 6160, 6159, 6158, 6445, 6157, 8592, 6156, 6155, 6167, 6168, 6198, 6196, 7653, 6195, 6229, 6202, 7840, 6201, 7641, 6200, 6182, 6181, 6180, 6179, 6189, 6945, 8952, 6974, 6355, 6356, 6353, 6354, 6357, 6358, 6410, 6412, 6413, 6438, 6450, 6621, 6186, 7620, 6626, 7664, 7661, 7687, 7867, 7660, 6176, 7698, 6290, 7916, 7975, 6173, 7995, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 8633, 8643, 8662, 6411, 8718, 8719, 8717, 8721, 8720, 10248.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 06 DE OCTUBRE DE 2026:
+Circuito : Pionero I desde BC - 950122.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Majes: Asentamiento B1, Avg Aspein, Avg Los Olivos, B-3, Corazon de Jesus, E - 8, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A-B-C, Modulo A Sector 5 Modulo C Sector 2, Nuevo Progreso C-2, Rafael Hoyos Rubio.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6194, 6250, 6187, 6197, 8818, 6184, 7665, 6183, 6165, 6164, 8904, 6193, 6192, 6191, 6190, 6203, 6444, 6622, 6188, 6206, 10215, 6205, 6204, 6185, 6199, 6172, 7654, 6171, 6515, 6170, 6169, 6154, 6963, 8886, 8889, 6266, 6280, 6166, 7820, 6625, 6177, 7705, 6432, 6178, 6175, 10251, 6174, 6582, 6163, 7919, 7911, 6162, 6161, 6160, 6159, 6158, 6445, 6157, 8592, 6156, 6155, 6167, 6168, 6198, 6196, 7653, 6195, 6229, 6202, 7840, 6201, 7641, 6200, 6182, 6181, 6180, 6179, 6189, 6945, 8952, 6974, 6355, 6356, 6353, 6354, 6357, 6358, 6410, 6412, 6413, 6438, 6450, 6621, 6186, 7620, 6626, 7664, 7661, 7687, 7867, 7660, 6176, 7698, 6290, 7916, 7975, 6173, 7995, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 8633, 8643, 8662, 6411, 8718, 8719, 8717, 8721, 8720, 10248.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 03/10/2026 8:45 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2026 8:45</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6076&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>dca5f4172fd8c41268538445d7f93df38c41bc9b879e932447390b3c74d6abc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6075</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Aptasa, Parque Industrial Rio Seco, Via Evitamiento.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [807] AVIACION.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2425, 2347, 3820, 3359, 2574, 1835, 1548, 2377, 4203, 4469, 4486, 4488, 5124, 5265, 5319, 5190, 5384, 5797, 5832, 10158.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 06 DE OCTUBRE DE 2026:
+Circuito : [807] AVIACION.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Aptasa, Parque Industrial Rio Seco, Via Evitamiento.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2425, 2347, 3820, 3359, 2574, 1835, 1548, 2377, 4203, 4469, 4486, 4488, 5124, 5265, 5319, 5190, 5384, 5797, 5832, 10158.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 03/10/2026 8:44 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2026 8:44</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6075&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>a5e7996de7a8b6681e6469e0aa445366ca786bc3b365c788bbb90f425ccce645</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Santa Rita de Siguas, de Santa Rita de Siguas</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Santa Rita desde REC - 200138.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 07 DE OCTUBRE DE 2026:
+Circuito : Santa Rita desde REC - 200138.
+Hora : 07:00 a 11:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 03/10/2026 8:46 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2026 8:46</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6078&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4dd08a6c0a16cc633a21a3289c1602e78c9abc33c90868cda50ed66d214c5b90</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6077</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Pastor</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de poste, inserción de nueva subestación).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cristo Rey desde REC - 200533.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 07 DE OCTUBRE DE 2026:
+Circuito : Cristo Rey desde REC - 200533.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de poste, inserción de nueva subestación).
+Zonas : Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 03/10/2026 8:45 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2026 8:45</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6077&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>489488920c86d8bcc394180df9a42ee3827cc419bf5ec8ac463ab80689745ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, de La Joya</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (Podado de árboles, limpieza de aisladores, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Panamericana desde REC - 200137.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 07 DE OCTUBRE DE 2026:
+Circuito : Panamericana desde REC - 200137.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (Podado de árboles, limpieza de aisladores, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 03/10/2026 8:43 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>03/10/2026 8:43</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6074&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6bcd954cfa0d152a4a40d065d2311335b3882e30ab4941c520bd4ebc720bf20a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,173 +1033,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02 16:17:26</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:45:18</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>REQUESTS_STATIC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03 14:45:18</t>
+          <t>2026-10-04 15:23:59</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04 15:23:59</t>
+          <t>2026-10-05 19:18:59</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:18:59</t>
+          <t>2026-10-06 16:50:33</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026 8:43</t>
+          <t>07/10/2026 8:13</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1006,12 +1006,428 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6bcd954cfa0d152a4a40d065d2311335b3882e30ab4941c520bd4ebc720bf20a</t>
+          <t>97b29986768024830585be00ddd1cd94a856e96ecedcf10de760683b65a61e47</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Lluta, Majes, Santa Isabel de Siguas, de Lluta, de Majes, de Santa Isabel de Siguas</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tension (instalación de poste, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [9603] PITAY.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 09 DE OCTUBRE DE 2026:
+Circuito : [9603] PITAY.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tension (instalación de poste, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 8:05 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 8:05</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6081&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>04f0cb84a7e359e09cc1b9347816cdfb2f999ec37bc0e22bd20f9a0fe65f7ab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6080</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Pastor, de Samuel Pastor</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de poste y conductor de media tensión.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : San Gregorio desde BC - 200128.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9052, 9051, 9094, 9195.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 09 DE OCTUBRE DE 2026:
+Circuito : San Gregorio desde BC - 200128.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de poste y conductor de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9052, 9051, 9094, 9195.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 8:04</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6080&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>78c6760e7d182d05c9c1f442159496e3a468413cfa58d5a8de18e78c89c70561</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6082</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Pastor</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Montaje y desmontaje de la subestación.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 9049.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+SÁBADO, 10 DE OCTUBRE DE 2026.
+Circuito : SED 9049.
+Hora : 07:30 a 13:30 Hrs.
+Motivo : Montaje y desmontaje de la subestación.
+Zonas afectadas: Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 8:06</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6082&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>a79a3a615f6a5637a1b78e51d774f8cb57ebf8c2141038ebae8050fc1c09e00f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6079</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Sosa Ruiz desde BC - 070213.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 09 DE OCTUBRE DE 2026:
+Circuito : Sosa Ruiz desde BC - 070213.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 8:04</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6079&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>555a30525a9ac5c237f663fa9d6a20f7d4e220347a2bdefa41bae1bd5bd7b199</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6083</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento del transformador de potencia y línea de transmisión.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA. SET : [16] REAL PLAZA.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 11 DE OCTUBRE DE 2026:
+LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA.
+SET : [16] REAL PLAZA.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento del transformador de potencia y línea de transmisión.
+Zonas afectadas: Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 8:06</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6083&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>63e296eec8181a1ed49a476fbba4f36c1912287ae2555440e7772b38a0349803</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1052,7 +1468,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 16:50:33</t>
+          <t>2026-10-07 17:27:12</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1492,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1504,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1516,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1564,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1576,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1588,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1615,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
-  <autoFilter ref="A1:P11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
+  <autoFilter ref="A1:P10"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Santa Rita de Siguas, de Santa Rita de Siguas</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Asentamiento B1, Avg Aspein, Avg Los Olivos, B-3, Corazon de Jesus, E - 8, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A-B-C, Modulo A Sector 5 Modulo C Sector 2, Nuevo Progreso C-2, Rafael Hoyos Rubio.</t>
+          <t>Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
+          <t>Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pionero I desde BC - 950122.</t>
+          <t>Circuito : Santa Rita desde REC - 200138.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,178 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6194, 6250, 6187, 6197, 8818, 6184, 7665, 6183, 6165, 6164, 8904, 6193, 6192, 6191, 6190, 6203, 6444, 6622, 6188, 6206, 10215, 6205, 6204, 6185, 6199, 6172, 7654, 6171, 6515, 6170, 6169, 6154, 6963, 8886, 8889, 6266, 6280, 6166, 7820, 6625, 6177, 7705, 6432, 6178, 6175, 10251, 6174, 6582, 6163, 7919, 7911, 6162, 6161, 6160, 6159, 6158, 6445, 6157, 8592, 6156, 6155, 6167, 6168, 6198, 6196, 7653, 6195, 6229, 6202, 7840, 6201, 7641, 6200, 6182, 6181, 6180, 6179, 6189, 6945, 8952, 6974, 6355, 6356, 6353, 6354, 6357, 6358, 6410, 6412, 6413, 6438, 6450, 6621, 6186, 7620, 6626, 7664, 7661, 7687, 7867, 7660, 6176, 7698, 6290, 7916, 7975, 6173, 7995, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 8633, 8643, 8662, 6411, 8718, 8719, 8717, 8721, 8720, 10248.</t>
+          <t>6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 06 DE OCTUBRE DE 2026:
-Circuito : Pionero I desde BC - 950122.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Majes: Asentamiento B1, Avg Aspein, Avg Los Olivos, B-3, Corazon de Jesus, E - 8, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A-B-C, Modulo A Sector 5 Modulo C Sector 2, Nuevo Progreso C-2, Rafael Hoyos Rubio.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6194, 6250, 6187, 6197, 8818, 6184, 7665, 6183, 6165, 6164, 8904, 6193, 6192, 6191, 6190, 6203, 6444, 6622, 6188, 6206, 10215, 6205, 6204, 6185, 6199, 6172, 7654, 6171, 6515, 6170, 6169, 6154, 6963, 8886, 8889, 6266, 6280, 6166, 7820, 6625, 6177, 7705, 6432, 6178, 6175, 10251, 6174, 6582, 6163, 7919, 7911, 6162, 6161, 6160, 6159, 6158, 6445, 6157, 8592, 6156, 6155, 6167, 6168, 6198, 6196, 7653, 6195, 6229, 6202, 7840, 6201, 7641, 6200, 6182, 6181, 6180, 6179, 6189, 6945, 8952, 6974, 6355, 6356, 6353, 6354, 6357, 6358, 6410, 6412, 6413, 6438, 6450, 6621, 6186, 7620, 6626, 7664, 7661, 7687, 7867, 7660, 6176, 7698, 6290, 7916, 7975, 6173, 7995, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 8633, 8643, 8662, 6411, 8718, 8719, 8717, 8721, 8720, 10248.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 03/10/2026 8:45 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>03/10/2026 8:45</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6076&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>dca5f4172fd8c41268538445d7f93df38c41bc9b879e932447390b3c74d6abc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6075</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Aptasa, Parque Industrial Rio Seco, Via Evitamiento.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [807] AVIACION.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2425, 2347, 3820, 3359, 2574, 1835, 1548, 2377, 4203, 4469, 4486, 4488, 5124, 5265, 5319, 5190, 5384, 5797, 5832, 10158.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 06 DE OCTUBRE DE 2026:
-Circuito : [807] AVIACION.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Aptasa, Parque Industrial Rio Seco, Via Evitamiento.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2425, 2347, 3820, 3359, 2574, 1835, 1548, 2377, 4203, 4469, 4486, 4488, 5124, 5265, 5319, 5190, 5384, 5797, 5832, 10158.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 03/10/2026 8:44 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>03/10/2026 8:44</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6075&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>a5e7996de7a8b6681e6469e0aa445366ca786bc3b365c788bbb90f425ccce645</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6078</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Santa Rita de Siguas, de Santa Rita de Siguas</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Santa Rita desde REC - 200138.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 07 DE OCTUBRE DE 2026:
@@ -820,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 03/10/2026 8:46 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>03/10/2026 8:46</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6078&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4dd08a6c0a16cc633a21a3289c1602e78c9abc33c90868cda50ed66d214c5b90</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6077</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>07/10/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de poste, inserción de nueva subestación).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cristo Rey desde REC - 200533.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 07 DE OCTUBRE DE 2026:
@@ -904,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 03/10/2026 8:45 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>03/10/2026 8:45</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6077&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>489488920c86d8bcc394180df9a42ee3827cc419bf5ec8ac463ab80689745ef8</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6074</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>07/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (Podado de árboles, limpieza de aisladores, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Panamericana desde REC - 200137.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 07 DE OCTUBRE DE 2026:
@@ -988,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 03/10/2026 8:43 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:13</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6074&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>97b29986768024830585be00ddd1cd94a856e96ecedcf10de760683b65a61e47</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6081</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Lluta, Majes, Santa Isabel de Siguas, de Lluta, de Majes, de Santa Isabel de Siguas</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tension (instalación de poste, podado de árboles).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9603] PITAY.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -1072,80 +904,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:05</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6081&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>04f0cb84a7e359e09cc1b9347816cdfb2f999ec37bc0e22bd20f9a0fe65f7ab2</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6080</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor, de Samuel Pastor</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de poste y conductor de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : San Gregorio desde BC - 200128.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9052, 9051, 9094, 9195.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -1156,76 +988,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9052, 9051, 9094, 9195.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:04</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6080&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>78c6760e7d182d05c9c1f442159496e3a468413cfa58d5a8de18e78c89c70561</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6082</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Montaje y desmontaje de la subestación.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 9049.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 10 DE OCTUBRE DE 2026.
@@ -1235,80 +1067,80 @@
 Zonas afectadas: Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:06</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6082&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>a79a3a615f6a5637a1b78e51d774f8cb57ebf8c2141038ebae8050fc1c09e00f</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6079</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Sosa Ruiz desde BC - 070213.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -1319,80 +1151,164 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:04</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6079&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>555a30525a9ac5c237f663fa9d6a20f7d4e220347a2bdefa41bae1bd5bd7b199</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>SET : [70] COTAHUASI.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 11 DE OCTUBRE DE 2026:
+SET : [70] COTAHUASI.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).
+Zonas afectadas: Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 07/10/2026 17:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 17:07</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6084&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8dfb11ba0ae371cc9c70ca1ad2114367e6a1d6fc29fd3617616f5f3051439881</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6083</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>11/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de potencia y línea de transmisión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA. SET : [16] REAL PLAZA.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 11 DE OCTUBRE DE 2026:
@@ -1404,30 +1320,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:06</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6083&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>63e296eec8181a1ed49a476fbba4f36c1912287ae2555440e7772b38a0349803</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1468,7 +1384,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27:12</t>
+          <t>2026-10-08 17:25:17</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1408,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1420,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1432,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1480,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1492,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1531,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
-  <autoFilter ref="A1:P10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,292 +608,40 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Santa Rita de Siguas, de Santa Rita de Siguas</t>
+          <t>Lluta, Majes, Santa Isabel de Siguas, de Lluta, de Majes, de Santa Isabel de Siguas</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.</t>
+          <t>Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).</t>
+          <t>Mantenimiento de redes de media tension (instalación de poste, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Santa Rita desde REC - 200138.</t>
+          <t>Circuito : [9603] PITAY.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
+          <t>6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 07 DE OCTUBRE DE 2026:
-Circuito : Santa Rita desde REC - 200138.
-Hora : 07:00 a 11:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (reubicación de subestación, retiro de postes, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Santa Rita de Siguas: Asoc. Viv. Nueva Juventud Zn C, Asoc. Viv. Taller Nueva Juventud Zn A, Asoc. Viv. Taller Nueva Juventud Zn B, Augusto Guilardi, Santa Rita de Sihuas, Villa San Antonio.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6242, 8831, 6252, 7700, 6225, 6219, 6218, 6216, 6215, 7892, 6214, 6213, 6437, 6212, 6251, 6264, 6248, 6240, 6221, 6220, 6231, 6236, 8943, 6241, 6223, 6222, 6246, 6224, 6941, 7953, 6361, 6360, 7668, 6311, 6312, 6313, 6314, 6433, 7915, 6315, 7891, 6316, 6420, 6421, 6414, 6416, 6415, 6417, 6418, 6448, 7663, 6217, 7838, 7978, 7979, 8948, 8532, 7672, 7951, 8846.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 03/10/2026 8:46 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>03/10/2026 8:46</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6078&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>4dd08a6c0a16cc633a21a3289c1602e78c9abc33c90868cda50ed66d214c5b90</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6077</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Samuel Pastor</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de poste, inserción de nueva subestación).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Cristo Rey desde REC - 200533.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 07 DE OCTUBRE DE 2026:
-Circuito : Cristo Rey desde REC - 200533.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de poste, inserción de nueva subestación).
-Zonas : Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 03/10/2026 8:45 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>03/10/2026 8:45</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6077&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>489488920c86d8bcc394180df9a42ee3827cc419bf5ec8ac463ab80689745ef8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>La Joya, de La Joya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (Podado de árboles, limpieza de aisladores, subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Panamericana desde REC - 200137.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 07 DE OCTUBRE DE 2026:
-Circuito : Panamericana desde REC - 200137.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (Podado de árboles, limpieza de aisladores, subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 03/10/2026 8:43 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:13</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6074&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>97b29986768024830585be00ddd1cd94a856e96ecedcf10de760683b65a61e47</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6081</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Lluta, Majes, Santa Isabel de Siguas, de Lluta, de Majes, de Santa Isabel de Siguas</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tension (instalación de poste, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [9603] PITAY.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -904,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:05</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6081&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>04f0cb84a7e359e09cc1b9347816cdfb2f999ec37bc0e22bd20f9a0fe65f7ab2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6080</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor, de Samuel Pastor</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de poste y conductor de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : San Gregorio desde BC - 200128.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9052, 9051, 9094, 9195.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -988,76 +736,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9052, 9051, 9094, 9195.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:04</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6080&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>78c6760e7d182d05c9c1f442159496e3a468413cfa58d5a8de18e78c89c70561</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6082</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Montaje y desmontaje de la subestación.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 9049.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 10 DE OCTUBRE DE 2026.
@@ -1067,80 +815,80 @@
 Zonas afectadas: Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:06</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6082&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>a79a3a615f6a5637a1b78e51d774f8cb57ebf8c2141038ebae8050fc1c09e00f</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6079</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Sosa Ruiz desde BC - 070213.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 09 DE OCTUBRE DE 2026:
@@ -1151,80 +899,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:04</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6079&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>555a30525a9ac5c237f663fa9d6a20f7d4e220347a2bdefa41bae1bd5bd7b199</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6084</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>11/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 11 DE OCTUBRE DE 2026:
@@ -1235,80 +983,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 17:07</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6084&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>8dfb11ba0ae371cc9c70ca1ad2114367e6a1d6fc29fd3617616f5f3051439881</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6083</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>11/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de potencia y línea de transmisión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA. SET : [16] REAL PLAZA.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 11 DE OCTUBRE DE 2026:
@@ -1320,30 +1068,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:06</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6083&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>63e296eec8181a1ed49a476fbba4f36c1912287ae2555440e7772b38a0349803</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1384,7 +1132,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:25:17</t>
+          <t>2026-10-09 17:00:56</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1156,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1168,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1180,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1252,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1279,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
+  <autoFilter ref="A1:P18"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1090,8 +1090,929 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Las Peñas desde BC - 041005.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+LUNES, 12 DE OCTUBRE DE 2026:
+Circuito : Las Peñas desde BC - 041005.
+Hora : 08:00 a 11:00 Hrs.
+Motivo :OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
+Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:12 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:12</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6085&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>93aeb9099bf00df50fc4e3dafa1828fc9925ebce020fa73f7a6168a1a322e1db</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6086</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [902] MARIATEGUI.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+LUNES, 12 DE OCTUBRE DE 2026:
+Circuito : [902] MARIATEGUI.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
+Zonas afectadas: Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:18 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:18</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6086&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>7cdab1fda98c03eaff37e6daef91cd3071ee608811c03c7bbeb4cd41813fd757</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Las Peñas desde BC - 041005.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+LUNES, 12 DE OCTUBRE DE 2026:
+Circuito : Las Peñas desde BC - 041005.
+Hora : 08:00 a 11:00 Hrs.
+Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
+Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:19 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6087&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>d8e445333dd49610c476c39194109e886c566d844f9c4e2a79e34825cee0264d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6090</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cotahuasi desde REC - 700116.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 13 DE OCTUBRE DE 2026:
+Circuito : Cotahuasi desde REC - 700116.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión y podado de árboles.
+Zonas afectadas: Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6090&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>c7300499568653ea83ef97c3f138d3e2f90811cec798fbcea0233919dbc27156</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6088</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Rio Seco.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Rio Seco desde REC - 200545.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 13 DE OCTUBRE DE 2026:
+Circuito : Rio Seco desde REC - 200545.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Rio Seco.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:20 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:20</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6088&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>6cdb92bcdf5030516a8c10f5e65ad2a40d47e0dd11e99aa33b23e63ea48cb808</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [904] GALAXIA.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MARTES, 13 DE OCTUBRE DE 2026:
+Circuito : [904] GALAXIA.
+Hora : 08:00 a 11:00 Hrs.
+Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
+Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:21 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:21</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6089&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4539b96c125e9e89ba59a1ce7ee5a0b8bb320da223f71c1efb1ad5f6ba3bdd86</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Jahuay desde REC - 200452.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 14 DE OCTUBRE DE 2026:
+Circuito : Jahuay desde REC - 200452.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Cocachacra, de Cocachacra</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 14 DE OCTUBRE DE 2026:
+LÍNEAS : [L-3038C] Cocachacra - Chucarapi.
+SET : [38] CHUCARAPI
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Cambio de armado en EAT43 y EAT 44 por DMS.
+Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:25</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, de La Joya</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Joya desde REC - 200431.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 14 DE OCTUBRE DE 2026:
+Circuito : La Joya desde REC - 200431.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:24</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6093</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Yanque, de Yanque</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Callalli 22.9 desde CC 200249.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9377.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MIÉRCOLES, 14 DE OCTUBRE DE 2026:
+Circuito : Callalli 22.9 desde CC 200249.
+Hora : 08:00 a 11:00 Hrs.
+Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa
+Zonas : Urbanizaciones del distrito de Yanque: Sector de Chollorota.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:24</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Yura, de Yura</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las líneas de media tensión.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde REC - 080306.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 15 DE OCTUBRE DE 2026:
+Circuito : P. Yura desde REC - 080306.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de las líneas de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026 10:26</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1132,7 +2053,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09 17:00:56</t>
+          <t>2026-10-10 15:53:26</t>
         </is>
       </c>
     </row>
@@ -1156,7 +2077,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1168,7 +2089,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1180,7 +2101,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
     </row>
@@ -1228,7 +2149,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1240,7 +2161,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +2173,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1279,7 +2200,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
-  <autoFilter ref="A1:P18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
+  <autoFilter ref="A1:P14"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lluta, Majes, Santa Isabel de Siguas, de Lluta, de Majes, de Santa Isabel de Siguas</t>
+          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.</t>
+          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tension (instalación de poste, podado de árboles).</t>
+          <t>Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [9603] PITAY.</t>
+          <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,341 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
+          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 09 DE OCTUBRE DE 2026:
-Circuito : [9603] PITAY.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tension (instalación de poste, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Lluta: La Quebrada. Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Centro de Servicios E-1, Ciudad de Majes Modulo B Sector 1, Ciudad de Majes Modulo B Sector 2-3, Ciudad de Majes Modulo F, E-2, El Paraiso, Modulo E Sector 1-2, Nueva Ciudad de Majes - Modulo A, Nuevo Horizonte. Urbanizaciones del distrito de Santa Isabel de Siguas: A.H.Ocoña, Cerro Blanco, La Quebrada, Laderas, Lluclla, Ocurunga San Bacilio, Rancheria, Sondor.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6273, 6281, 6282, 6283, 6284, 6285, 6286, 6287, 6233, 6234, 6226, 6267, 6265, 6274, 6272, 6262, 6263, 6259, 6271, 6257, 6258, 6249, 6288, 6300, 6321, 6000, 6322, 6323, 6324, 6325, 6326, 6327, 6328, 6329, 6330, 10226, 6332, 6333, 6334, 6335, 6336, 6337, 6338, 6339, 6340, 6341, 6436, 6495, 6466, 6467, 6492, 6468, 6464, 6485, 6463, 6462, 6491, 6490, 6465, 6474, 6475, 6473, 6472, 6469, 6483, 6508, 6504, 6499, 6496, 6509, 6505, 6500, 6497, 6510, 6506, 6501, 6498, 6511, 6513, 6502, 6503, 6512, 6507, 7628, 7817, 7843, 8881, 8841, 8902, 8970, 8971, 8972, 8522, 8523, 8524, 8525, 8526, 8963, 8962, 8515, 8516, 8517, 8518, 8514, 8840, 8641, 8670, 10048, 8759, 8762, 8760, 8761, 10276, 10288.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 8:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:05</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6081&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>04f0cb84a7e359e09cc1b9347816cdfb2f999ec37bc0e22bd20f9a0fe65f7ab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Samuel Pastor, de Samuel Pastor</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de poste y conductor de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : San Gregorio desde BC - 200128.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9052, 9051, 9094, 9195.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 09 DE OCTUBRE DE 2026:
-Circuito : San Gregorio desde BC - 200128.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de poste y conductor de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Samuel Pastor: San Benito de Palermo.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9052, 9051, 9094, 9195.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:04</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6080&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>78c6760e7d182d05c9c1f442159496e3a468413cfa58d5a8de18e78c89c70561</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6082</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Samuel Pastor</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Montaje y desmontaje de la subestación.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 9049.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-SÁBADO, 10 DE OCTUBRE DE 2026.
-Circuito : SED 9049.
-Hora : 07:30 a 13:30 Hrs.
-Motivo : Montaje y desmontaje de la subestación.
-Zonas afectadas: Mz. A-B-C-I de la Zona A de Urb. El Carmen (Distrito Samuel Pastor).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6082&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>a79a3a615f6a5637a1b78e51d774f8cb57ebf8c2141038ebae8050fc1c09e00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6079</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Sosa Ruiz desde BC - 070213.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 09 DE OCTUBRE DE 2026:
-Circuito : Sosa Ruiz desde BC - 070213.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apgv La Estrella del Cural, Crucero La Estrella 1, Irrigacion El Cural Lateral 6-8.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1382, 1870, 4376, 10332, 3837, 1815, 5019, 2133, 3926, 4281, 4439, 5605, 4960, 4767, 5527, 5528, 5529, 5530, 3346, 5807, 5911.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:04</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6079&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>555a30525a9ac5c237f663fa9d6a20f7d4e220347a2bdefa41bae1bd5bd7b199</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6084</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>11/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SET : [70] COTAHUASI.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 11 DE OCTUBRE DE 2026:
@@ -983,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 17:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 17:07</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6084&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>8dfb11ba0ae371cc9c70ca1ad2114367e6a1d6fc29fd3617616f5f3051439881</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6083</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>11/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de potencia y línea de transmisión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA. SET : [16] REAL PLAZA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 11 DE OCTUBRE DE 2026:
@@ -1068,80 +737,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>07/10/2026 8:06</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6083&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>63e296eec8181a1ed49a476fbba4f36c1912287ae2555440e7772b38a0349803</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6085</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -1152,76 +821,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:12</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6085&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>93aeb9099bf00df50fc4e3dafa1828fc9925ebce020fa73f7a6168a1a322e1db</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6086</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : [902] MARIATEGUI.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -1232,80 +901,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:18</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6086&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>7cdab1fda98c03eaff37e6daef91cd3071ee608811c03c7bbeb4cd41813fd757</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6087</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -1316,80 +985,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:19</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6087&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>d8e445333dd49610c476c39194109e886c566d844f9c4e2a79e34825cee0264d</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6090</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cotahuasi desde REC - 700116.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1400,80 +1069,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6090&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>c7300499568653ea83ef97c3f138d3e2f90811cec798fbcea0233919dbc27156</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6088</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Rio Seco.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Rio Seco desde REC - 200545.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1484,80 +1153,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:20</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6088&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>6cdb92bcdf5030516a8c10f5e65ad2a40d47e0dd11e99aa33b23e63ea48cb808</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6089</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : [904] GALAXIA.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1568,80 +1237,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:21</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6089&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>4539b96c125e9e89ba59a1ce7ee5a0b8bb320da223f71c1efb1ad5f6ba3bdd86</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6091</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1652,80 +1321,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6094</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1737,80 +1406,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:25</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6092</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Joya desde REC - 200431.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1821,80 +1490,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6093</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Yanque, de Yanque</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC 200249.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9377.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1905,80 +1574,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>15/10/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las líneas de media tensión.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde REC - 080306.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 15 DE OCTUBRE DE 2026:
@@ -1989,30 +1658,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:26</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18"/>
+  <autoFilter ref="A1:P14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2053,7 +1722,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 15:53:26</t>
+          <t>2026-10-11 16:20:38</t>
         </is>
       </c>
     </row>
@@ -2077,7 +1746,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2089,7 +1758,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -2101,7 +1770,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
     </row>
@@ -2173,7 +1842,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +1869,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:20:38</t>
+          <t>2026-10-12 19:49:50</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,224 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
+          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
+          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).</t>
+          <t>OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET : [70] COTAHUASI.</t>
+          <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 11 DE OCTUBRE DE 2026:
-SET : [70] COTAHUASI.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (tendido de línea de guarda, cambio de postes, podado de árboles).
-Zonas afectadas: Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 17:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 17:07</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6084&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>8dfb11ba0ae371cc9c70ca1ad2114367e6a1d6fc29fd3617616f5f3051439881</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6083</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>11/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento del transformador de potencia y línea de transmisión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA. SET : [16] REAL PLAZA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 11 DE OCTUBRE DE 2026:
-LÍNEA : [L-3063] CHALLAPAMPA-REAL PLAZA.
-SET : [16] REAL PLAZA.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento del transformador de potencia y línea de transmisión.
-Zonas afectadas: Urbanizaciones del distrito de Cayma: Leon XIII, Los Sauces. Urbanizaciones del distrito de Cerro Colorado: 12 de Octubre, Cerrito Los Alvarez, Cerro Colorado (Pueblo Viejo), Santa Rosa de Lima, Villa El Sol. Urbanizaciones del distrito de Yanahuara: Buena Vista, Cooperativa Entel Peru, Entel Peru, Independencia Americana, Juan Xxiii, Las Casuarinas, Las Condes, Las Orquideas, Los Cedros, Los Gladiolos, Magisterial III, Piedra Santa I, Piedra Santa II, Primavera, Quinta La Estancia, Quinta Los Gladiolos, Quinta Residencial Texao, Residencial El Chullo, San Rafael, Santa Beatriz, Santa Cecilia, Valencia, Victor Andres Belaunde, Yanahuara.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1228, 2624, 2351, 2315, 2318, 2303, 1257, 2666, 1222, 3543, 2443, 2442, 2304, 2471, 4235, 5068, 5717, 2312, 10144, 4465, 4548, 4549, 4550, 1732, 2116, 1230, 2995, 2598, 1238, 1430, 2344, 1842, 1237, 1355, 1219, 1669, 2350, 1572, 1853, 1508, 2345, 4662, 5005, 5260, 4952, 5236, 5666, 2157, 5119, 5106, 5339, 5054, 5070, 3954, 1529, 2623, 3432, 2758, 3845, 3880, 2308, 2306, 2302, 2721, 1633, 3834, 2715, 1455, 1229, 2759, 2760, 2649, 1646, 4328, 4630, 5168, 5349, 5718, 5844, 4211, 5940, 10240, 10324, 10266, 10243.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 07/10/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6083&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>63e296eec8181a1ed49a476fbba4f36c1912287ae2555440e7772b38a0349803</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Las Peñas desde BC - 041005.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -821,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:12</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6085&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>93aeb9099bf00df50fc4e3dafa1828fc9925ebce020fa73f7a6168a1a322e1db</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6086</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [902] MARIATEGUI.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -901,80 +732,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:18 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:18</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6086&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>7cdab1fda98c03eaff37e6daef91cd3071ee608811c03c7bbeb4cd41813fd757</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6087</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 LUNES, 12 DE OCTUBRE DE 2026:
@@ -985,80 +816,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:19</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6087&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>d8e445333dd49610c476c39194109e886c566d844f9c4e2a79e34825cee0264d</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6090</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cotahuasi desde REC - 700116.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1069,80 +900,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6090&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>c7300499568653ea83ef97c3f138d3e2f90811cec798fbcea0233919dbc27156</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6088</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Rio Seco.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Rio Seco desde REC - 200545.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1153,80 +984,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:20</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6088&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>6cdb92bcdf5030516a8c10f5e65ad2a40d47e0dd11e99aa33b23e63ea48cb808</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6089</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [904] GALAXIA.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1237,80 +1068,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:21</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6089&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>4539b96c125e9e89ba59a1ce7ee5a0b8bb320da223f71c1efb1ad5f6ba3bdd86</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6091</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1321,80 +1152,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6094</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1406,80 +1237,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:25</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6092</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Joya desde REC - 200431.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1490,80 +1321,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6093</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Yanque, de Yanque</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC 200249.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>9377.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1574,80 +1405,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>15/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las líneas de media tensión.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde REC - 080306.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 15 DE OCTUBRE DE 2026:
@@ -1658,30 +1489,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:26</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1722,7 +1553,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 19:49:50</t>
+          <t>2026-10-13 17:37:19</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1577,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1589,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1601,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1673,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1700,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,303 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
+          <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
+          <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
+          <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Las Peñas desde BC - 041005.</t>
+          <t>Circuito : Cotahuasi desde REC - 700116.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>REFORZAMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+          <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-LUNES, 12 DE OCTUBRE DE 2026:
-Circuito : Las Peñas desde BC - 041005.
-Hora : 08:00 a 11:00 Hrs.
-Motivo :OBRA “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
-Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:12 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:12</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6085&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>93aeb9099bf00df50fc4e3dafa1828fc9925ebce020fa73f7a6168a1a322e1db</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [902] MARIATEGUI.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-LUNES, 12 DE OCTUBRE DE 2026:
-Circuito : [902] MARIATEGUI.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
-Zonas afectadas: Urbanizaciones de Alto Selva Alegre: El Gran Chaparral, El Mirador Primera Etapa, El Mirador Segunda Etapa, Huarangal, Independencia Zona A, Independencia Zona B, Lealtad Democratica, Los Angeles del Misti, Tres Balcones del Misti, Villa Asuncion, Villa Chachas, Villa Esperanza, Villa Independiente Zona A, Villa San Pablo.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2406, 3896, 1768, 3440, 1901, 3229, 3439, 1538, 1718, 2405, 3466, 3465, 3686, 4000, 4102, 4103, 4104, 4105, 4301, 4459, 4414, 4504, 4505, 4937, 4918, 5051, 5428, 5657, 5679, 5811, 5942, 10020, 10021, 2407, 5464, 10377.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:18 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:18</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6086&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>7cdab1fda98c03eaff37e6daef91cd3071ee608811c03c7bbeb4cd41813fd757</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6087</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Las Peñas desde BC - 041005.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-LUNES, 12 DE OCTUBRE DE 2026:
-Circuito : Las Peñas desde BC - 041005.
-Hora : 08:00 a 11:00 Hrs.
-Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
-Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:19 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:19</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6087&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>d8e445333dd49610c476c39194109e886c566d844f9c4e2a79e34825cee0264d</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Cotahuasi desde REC - 700116.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -900,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6090&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>c7300499568653ea83ef97c3f138d3e2f90811cec798fbcea0233919dbc27156</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6088</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Rio Seco.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Rio Seco desde REC - 200545.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -984,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:20</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6088&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>6cdb92bcdf5030516a8c10f5e65ad2a40d47e0dd11e99aa33b23e63ea48cb808</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6089</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>13/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : [904] GALAXIA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MARTES, 13 DE OCTUBRE DE 2026:
@@ -1068,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:21</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6089&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>4539b96c125e9e89ba59a1ce7ee5a0b8bb320da223f71c1efb1ad5f6ba3bdd86</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6091</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1152,80 +904,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6094</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1237,80 +989,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:25</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6092</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Joya desde REC - 200431.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1321,80 +1073,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6093</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Yanque, de Yanque</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC 200249.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>9377.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1405,80 +1157,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>15/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las líneas de media tensión.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde REC - 080306.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 15 DE OCTUBRE DE 2026:
@@ -1489,30 +1241,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:26</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1553,7 +1305,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 17:37:19</t>
+          <t>2026-10-14 15:11:43</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1329,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1341,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1353,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1425,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1452,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,307 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Charcana, Cotahuasi, Pampamarca, Quechualla, Toro, de Charcana, de Cotahuasi, de Pampamarca, de Quechualla, de Toro</t>
+          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.</t>
+          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Cotahuasi desde REC - 700116.</t>
+          <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
+          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 13 DE OCTUBRE DE 2026:
-Circuito : Cotahuasi desde REC - 700116.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión y podado de árboles.
-Zonas afectadas: Urbanizaciones del distrito de Charcana: Andamarca, Ayapallpa, Charcana. Urbanizaciones del distrito de Cotahuasi: Ancaro. Urbanizaciones del distrito de Pampamarca: Lancaroya. Urbanizaciones del distrito de Quechualla: Allancay, Chaupo, Picha, Quechualla, Sancay, Velinga. Urbanizaciones del distrito de Toro: Caspi, Cupe, Huachuy, Llallihua, Shiringay, Toro.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7329, 7331, 7328, 7327, 7330, 7341, 7339, 7344, 7644, 7737, 7740, 7741, 7743, 7742, 7745, 7739, 7744, 7738, 7736, 7345, 7340, 9403.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:22</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6090&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>c7300499568653ea83ef97c3f138d3e2f90811cec798fbcea0233919dbc27156</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Rio Seco.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Rio Seco desde REC - 200545.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 13 DE OCTUBRE DE 2026:
-Circuito : Rio Seco desde REC - 200545.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Rio Seco.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 1492, 2670, 2687, 3383, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 2226, 4303, 4304, 4899, 5342, 5344, 5343, 5392, 2643, 10213, 10285.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:20</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6088&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>6cdb92bcdf5030516a8c10f5e65ad2a40d47e0dd11e99aa33b23e63ea48cb808</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Alto Selva Alegre, Mariano Melgar, Miraflores, de Alto Selva Alegre, de Mariano Melgar, de Miraflores</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [904] GALAXIA.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MARTES, 13 DE OCTUBRE DE 2026:
-Circuito : [904] GALAXIA.
-Hora : 08:00 a 11:00 Hrs.
-Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa.
-Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Asociacion de Granjeros San Lazaro y Pequeños Industriales, Bella Esperanza, Bella Esperanza Ampliacion Zona A y B, Javier Heraud, Prog Municipal de Pequeña Industria. Urbanizaciones del distrito de Mariano Melgar: A. H. Berlin II, A.H. Berlin, El Mirador Zona I, El Mirador Zona II, El Mirador Zona III, Pequeños Talleres Sr. de Los Milagros Zona IV, Pueblo Libre, San Francisco de Asis. Urbanizaciones del distrito de Miraflores: C. Granja Viv. San Lazaro Zona A, Los Girasoles II, Los Girasoles Zona B, Nuevo Amanecer, San Francisco de Asis.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3758, 1182, 2587, 3354, 3375, 3376, 3643, 3630, 2588, 4050, 4413, 4530, 4566, 4840, 4771, 4770, 4772, 5092, 5091, 5173, 5525, 5526, 5550, 3642, 3641, 4049, 10340.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:21 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:21</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6089&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4539b96c125e9e89ba59a1ce7ee5a0b8bb320da223f71c1efb1ad5f6ba3bdd86</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Jahuay desde REC - 200452.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -904,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:22</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6094</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -989,80 +737,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:25</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6092</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Joya desde REC - 200431.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1073,80 +821,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6093</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>14/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Yanque, de Yanque</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Callalli 22.9 desde CC 200249.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>9377.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 14 DE OCTUBRE DE 2026:
@@ -1157,80 +905,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:24</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>15/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las líneas de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde REC - 080306.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 15 DE OCTUBRE DE 2026:
@@ -1241,30 +989,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:26</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1305,7 +1053,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 15:11:43</t>
+          <t>2026-10-15 15:05:08</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1077,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1089,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1101,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1173,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1200,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
+  <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
+          <t>Yura, de Yura</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
+          <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).</t>
+          <t>Mantenimiento de las líneas de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Jahuay desde REC - 200452.</t>
+          <t>Circuito : P. Yura desde REC - 080306.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,347 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+          <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 14 DE OCTUBRE DE 2026:
-Circuito : Jahuay desde REC - 200452.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de transformador, subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:22 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:22</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6091&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>e8e089a45c564c215e5ce159a5160514036d8128d64cb76a795b193def579a8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6094</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra, de Cocachacra</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de armado en EAT43 y EAT 44 por DMS.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEAS : [L-3038C] Cocachacra - Chucarapi. SET : [38] CHUCARAPI</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 14 DE OCTUBRE DE 2026:
-LÍNEAS : [L-3038C] Cocachacra - Chucarapi.
-SET : [38] CHUCARAPI
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Cambio de armado en EAT43 y EAT 44 por DMS.
-Zonas : Urbanizaciones del Distrito de Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Chucarapi, Desamparados, El Fiscal, El Toro, La Pascana, Pampa Blanca, Portal del Valle.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657, 8217, 8223, 8221, 8218, 8219, 8258, 8264, 8283, 8276, 8222, 8246, 8216, 8277, 8263, 8303, 8304, 8305, 8318, 8319, 8320, 8312, 8313, 8314, 8315, 8316, 8317, 8324, 8339, 8340, 8306, 8370, 8372, 8378, 8389, 8436, 8508, 8542, 8598, 8618, 8512, 8737, 8224, 8513.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:25 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:25</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6094&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>f91ffedf42f44517f8a75a9e2bb091aac50a5792ea75484555e6604109b3bb58</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6092</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>La Joya, de La Joya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : La Joya desde REC - 200431.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 14 DE OCTUBRE DE 2026:
-Circuito : La Joya desde REC - 200431.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de las redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de La Joya: Cerrito Buena Vista, La Joya Antigua Sector 1, La Joya Antigua Sector 3, Las Dunas, Los Girasoles de La Joya, Los Laureles, Los Milagros, Los Patriotas, Mirador La Victoria, Mirador La Victoria II, Palca, Primavera.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6813, 6732, 6714, 6713, 6712, 6711, 6710, 6709, 8634, 6807, 6819, 6820, 6708, 6704, 6893, 6702, 6701, 7635, 6705, 6707, 6706, 6524, 6806, 6856, 6985, 6946, 6528, 7823, 6540, 6545, 6537, 6538, 6562, 6563, 6527, 6589, 6570, 8875, 6593, 6599, 7981, 4788, 4789, 8554, 7939, 7976, 8919, 8918, 8920, 8568, 4804, 8617, 8713, 8781, 9437.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:24</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6092&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>effc562fdfb72abda3d56f368bc81f936fc37a15336f1235367bbdb4418692f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6093</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Yanque, de Yanque</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Yanque: Sector de Chollorota.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Callalli 22.9 desde CC 200249.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9377.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MIÉRCOLES, 14 DE OCTUBRE DE 2026:
-Circuito : Callalli 22.9 desde CC 200249.
-Hora : 08:00 a 11:00 Hrs.
-Motivo : Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa
-Zonas : Urbanizaciones del distrito de Yanque: Sector de Chollorota.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9377.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 10/10/2026 10:24 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10/10/2026 10:24</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6093&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6d5de6ee46d54774b3dbf6b74a709efc389cc4f87af5c215e80a0baa714de10c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6095</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Yura, de Yura</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de las líneas de media tensión.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde REC - 080306.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 15 DE OCTUBRE DE 2026:
@@ -989,30 +652,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/10/2026 10:26</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1053,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:05:08</t>
+          <t>2026-10-16 14:54:00</t>
         </is>
       </c>
     </row>
@@ -1077,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1089,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1101,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
     </row>
@@ -1173,7 +836,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1200,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
+  <autoFilter ref="A1:P18"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,74 +608,1379 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yura, de Yura</t>
+          <t>Samuel Pastor</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.</t>
+          <t>Urbanizaciones del Distrito Samuel Pastor: A.H. Alta Vista, A.H. Alto Luren, A.H. Taller Huaco, Aa.Hh. Bella Union, Almirante Grau, Alto Buenos Aires, Centro Poblado Linares, Cristo Rey, Habitad For Humanity, La Rinconada, Los Olivos, Pueblo Nuevo, Señor de Luren, Villa Don Jorge, Villa Mrina, Virgen de La Candelaria.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de las líneas de media tensión.</t>
+          <t>Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : P. Yura desde REC - 080306.</t>
+          <t>Circuito : [4007] CRISTO REY.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
+          <t>9193, 9192, 9118, 9119, 9169, 9129, 9226, 9227, 9228, 9225, 9224, 9223, 9222, 9231, 9266, 9274, 9275, 9289, 9290, 9306, 9307, 9318, 9333, 9340, 9341, 9330, 9331, 9369.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 15 DE OCTUBRE DE 2026:
-Circuito : P. Yura desde REC - 080306.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de las líneas de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Yura: Balneario de Yura, El Filtro, Porvenir de Yura, Pueblo de Yura, Pueblo La Estacion de Yura.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3492, 3491, 3707, 3571, 4207, 3490, 4589, 4994.</t>
+          <t>REFORZAMIENTO DE REDES.
+VIERNES, 16 DE OCTUBRE DE 2026:
+Circuito : [4007] CRISTO REY.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
+Zonas : Urbanizaciones del Distrito Samuel Pastor: A.H. Alta Vista, A.H. Alto Luren, A.H. Taller Huaco, Aa.Hh. Bella Union, Almirante Grau, Alto Buenos Aires, Centro Poblado Linares, Cristo Rey, Habitad For Humanity, La Rinconada, Los Olivos, Pueblo Nuevo, Señor de Luren, Villa Don Jorge, Villa Mrina, Virgen de La Candelaria.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9192, 9118, 9119, 9169, 9129, 9226, 9227, 9228, 9225, 9224, 9223, 9222, 9231, 9266, 9274, 9275, 9289, 9290, 9306, 9307, 9318, 9333, 9340, 9341, 9330, 9331, 9369.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>el 10/10/2026 10:26 por Cuenta del sistema</t>
+          <t>el 16/10/2026 14:45 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>10/10/2026 10:26</t>
+          <t>16/10/2026 14:45</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6095&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6100&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>b636e756a03b9d83e93d2a114dd61fe27bd47566ba6e4fb0770a9c9c778944a9</t>
+          <t>78bc30a8ed5f1af7df65a842ed7771e3549e98448fc80ed7516f190fd24d8d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Jahuay desde REC - 200452.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+VIERNES, 16 DE OCTUBRE DE 2026:
+Circuito : Jahuay desde REC - 200452.
+Hora : 08:00 a 11:00 Hrs.
+Motivo : Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
+Zonas afectadas: Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 14:46 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 14:46</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6101&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>094e6392da8edcbe811a841261c52f39fcce133be2da9eea2652a17172699a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Florida desde REC - 200284.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+DOMINGO, 18 DE OCTUBRE DE 2026:
+Circuito : La Florida desde REC - 200284.
+Hora : 07:00 a 16:00 Hrs.
+Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 11:51</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6097&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6fed2ddd39cb04f2c4bb410d074ab0e70f77fcd95df52f708e0f9f58b8dd3f9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6098</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Alto Bellavista, Alto San Martin, Apvis Los Olivos del Puerto, Bellavista, Los Pinos, Obreros Municipales, San Martin, Villa Lourdes 2 Etapa, Villa Magisterial.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Hospital desde REC - 200136.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+DOMINGO, 18 DE OCTUBRE DE 2026:
+Circuito : Hospital desde REC - 200136.
+Hora : 07:00 a 16:00 Hrs.
+Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Alto Bellavista, Alto San Martin, Apvis Los Olivos del Puerto, Bellavista, Los Pinos, Obreros Municipales, San Martin, Villa Lourdes 2 Etapa, Villa Magisterial.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 11:51</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6098&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>58ebc0a7d301f082487a4adfea231c5b196f4d9f9d3c6d720aa29dff4cb18ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6096</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Aptasa, Centro Comercial Las Malvinas, Cooperativa Ex San Jose Obrero, La Cuarentenaria, Parque Industrial Rio Seco, Rio Seco, Santa Maria.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de equipo de maniobra.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Rio Seco desde BC - 080104.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 18 DE OCTUBRE DE 2026:
+Circuito : Rio Seco desde BC - 080104.
+Hora : 08:00 a 10:00 Hrs.
+Motivo : Cambio de equipo de maniobra.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Aptasa, Centro Comercial Las Malvinas, Cooperativa Ex San Jose Obrero, La Cuarentenaria, Parque Industrial Rio Seco, Rio Seco, Santa Maria.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 10:42 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 10:42</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6096&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6c883ab253447b80dcc88768cfd341fa0fc228dafdb7c7a7142fbe273754f333</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Apiamo, Bellavista, Catarindo, Centenario, Cercado de Mollendo, Estibadores, Inclán, La Florida, Los Delfines de Mollendo, Los Tres Portales, San Agustín Arvidunsa, Señor del Rímac.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento del transformador de potencia y line de transmisión.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA : [L-3031] BASE ISLAY-MOLLENDO. SET : [31] MOLLENDO.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 18 DE OCTUBRE DE 2026:
+LÍNEA : [L-3031] BASE ISLAY-MOLLENDO.
+SET : [31] MOLLENDO.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento del transformador de potencia y line de transmisión.
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Apiamo, Bellavista, Catarindo, Centenario, Cercado de Mollendo, Estibadores, Inclán, La Florida, Los Delfines de Mollendo, Los Tres Portales, San Agustín Arvidunsa, Señor del Rímac.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 11:52 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 11:52</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6099&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>f8cb4dbbf73699c5cdb55ac77b37a3a9884ec3cd179f77f5387f54c689405d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pitay desde CC - 950326.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 20 DE OCTUBRE DE 2026:
+Circuito : Pitay desde CC - 950326.
+Hora : 07:05 a 15:05 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:33 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:33</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6102&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>82bf4faf5ded6db465c0745defc3930a696e88d4d33ddf0f210ccd0de0777097</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Sachaca, de Sachaca</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2988.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 20 DE OCTUBRE DE 2026.
+Circuito : SED 2988.
+Hora : 08:30 a 08:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:34</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6103&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>f0d91a010a540a1e80128ca22b7b8d75f685b3faedf907a0db23e1bbef52a91a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 10337.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 20 DE OCTUBRE DE 2026.
+Circuito : SED 10337.
+Hora : 11:00 a 11:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:34</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6104&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>51490abb4e2fdad5b9baa4104f7c32f8304c90ecf9bae88db576055162e3d58f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1294.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 20 DE OCTUBRE DE 2026.
+Circuito : SED 1294.
+Hora : 11:50 a 12:10 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:35 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:35</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6105&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>7d988d85147c853dabc84fee8bb12cdaaec86331eb4eeab6bc9be34c7b81d6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Paucarpata, de Paucarpata</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2273.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 20 DE OCTUBRE DE 2026.
+Circuito : SED 2273.
+Hora : 14:00 a 14:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:36</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6106&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0dc0b5a6576d0ca862495ca0bfc716c87f0654909fb6561e21a349396ebb9314</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Colina desde REC - 950145.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MIERCOLES, 21 DE OCTUBRE DE 2026:
+Circuito : La Colina desde REC - 950145.
+Hora : 06:00 a 15:00 Hrs.
+Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
+Zonas afectadas: Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:39 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:39</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6112&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>d9bf4e25cfee750fde0f10344839c63569afbe87d18cfd10c7e21f86c8d3b099</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [808] AUTOPISTA.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 21 DE OCTUBRE DE 2026:
+Circuito : [808] AUTOPISTA.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:38</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6111&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>f6de992ab89cef5ca98439ac389dca9ca1b0e896e777db0f9dbe1f408f5f432f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3586.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 22 DE OCTUBRE DE 2026.
+Circuito : SED 3586.
+Hora : 05:00 a 05:30 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:38</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la subestación.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3645.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 22 DE OCTUBRE DE 2026.
+Circuito : SED 3645.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento de la subestación.
+Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:36</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la subestación.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3553.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 22 DE OCTUBRE DE 2026.
+Circuito : SED 3553.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento de la subestación.
+Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:37</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Mariano Melgar, de Mariano Melgar</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de tablero de distribución.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3079.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 22 DE OCTUBRE DE 2026.
+Circuito : SED 3079.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de tablero de distribución.
+Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:37</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>ad4ee179ccca6b22909b8028d1f8384fb511a972f6d5fe5349c30ebfc3a17fb7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -716,7 +2021,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 14:54:00</t>
+          <t>2026-10-17 13:45:50</t>
         </is>
       </c>
     </row>
@@ -740,7 +2045,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -752,7 +2057,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -764,7 +2069,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
     </row>
@@ -812,7 +2117,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -824,7 +2129,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -836,7 +2141,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -863,7 +2168,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
-  <autoFilter ref="A1:P18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P16" headerRowCount="1">
+  <autoFilter ref="A1:P16"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Samuel Pastor</t>
+          <t>Mollendo, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del Distrito Samuel Pastor: A.H. Alta Vista, A.H. Alto Luren, A.H. Taller Huaco, Aa.Hh. Bella Union, Almirante Grau, Alto Buenos Aires, Centro Poblado Linares, Cristo Rey, Habitad For Humanity, La Rinconada, Los Olivos, Pueblo Nuevo, Señor de Luren, Villa Don Jorge, Villa Mrina, Virgen de La Candelaria.</t>
+          <t>Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [4007] CRISTO REY.</t>
+          <t>Circuito : La Florida desde REC - 200284.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,178 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9193, 9192, 9118, 9119, 9169, 9129, 9226, 9227, 9228, 9225, 9224, 9223, 9222, 9231, 9266, 9274, 9275, 9289, 9290, 9306, 9307, 9318, 9333, 9340, 9341, 9330, 9331, 9369.</t>
+          <t>8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-VIERNES, 16 DE OCTUBRE DE 2026:
-Circuito : [4007] CRISTO REY.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
-Zonas : Urbanizaciones del Distrito Samuel Pastor: A.H. Alta Vista, A.H. Alto Luren, A.H. Taller Huaco, Aa.Hh. Bella Union, Almirante Grau, Alto Buenos Aires, Centro Poblado Linares, Cristo Rey, Habitad For Humanity, La Rinconada, Los Olivos, Pueblo Nuevo, Señor de Luren, Villa Don Jorge, Villa Mrina, Virgen de La Candelaria.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9192, 9118, 9119, 9169, 9129, 9226, 9227, 9228, 9225, 9224, 9223, 9222, 9231, 9266, 9274, 9275, 9289, 9290, 9306, 9307, 9318, 9333, 9340, 9341, 9330, 9331, 9369.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 14:45 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 14:45</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6100&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>78bc30a8ed5f1af7df65a842ed7771e3549e98448fc80ed7516f190fd24d8d79</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6101</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Jahuay desde REC - 200452.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-VIERNES, 16 DE OCTUBRE DE 2026:
-Circuito : Jahuay desde REC - 200452.
-Hora : 08:00 a 11:00 Hrs.
-Motivo : Obra: “Ampliación de redes de distribución primaria, secundaria y alumbrado público en 07 localidades ubicadas entre las provincias de Camaná, Caylloma y Arequipa dentro de la región de Arequipa”.
-Zonas afectadas: Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 14:46 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 14:46</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6101&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>094e6392da8edcbe811a841261c52f39fcce133be2da9eea2652a17172699a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : La Florida desde REC - 200284.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 DOMINGO, 18 DE OCTUBRE DE 2026:
@@ -820,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 11:51</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6097&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>6fed2ddd39cb04f2c4bb410d074ab0e70f77fcd95df52f708e0f9f58b8dd3f9c</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6098</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>18/10/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Alto Bellavista, Alto San Martin, Apvis Los Olivos del Puerto, Bellavista, Los Pinos, Obreros Municipales, San Martin, Villa Lourdes 2 Etapa, Villa Magisterial.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Hospital desde REC - 200136.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 DOMINGO, 18 DE OCTUBRE DE 2026:
@@ -904,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 11:51</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6098&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>58ebc0a7d301f082487a4adfea231c5b196f4d9f9d3c6d720aa29dff4cb18ff3</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6096</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>18/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Aptasa, Centro Comercial Las Malvinas, Cooperativa Ex San Jose Obrero, La Cuarentenaria, Parque Industrial Rio Seco, Rio Seco, Santa Maria.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de equipo de maniobra.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Rio Seco desde BC - 080104.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 18 DE OCTUBRE DE 2026:
@@ -988,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 10:42 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 10:42</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6096&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>6c883ab253447b80dcc88768cfd341fa0fc228dafdb7c7a7142fbe273754f333</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6099</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>18/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Apiamo, Bellavista, Catarindo, Centenario, Cercado de Mollendo, Estibadores, Inclán, La Florida, Los Delfines de Mollendo, Los Tres Portales, San Agustín Arvidunsa, Señor del Rímac.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de potencia y line de transmisión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : [L-3031] BASE ISLAY-MOLLENDO. SET : [31] MOLLENDO.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 18 DE OCTUBRE DE 2026:
@@ -1073,80 +905,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 11:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 11:52</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6099&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>f8cb4dbbf73699c5cdb55ac77b37a3a9884ec3cd179f77f5387f54c689405d3f</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 950326.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026:
@@ -1157,76 +989,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:33 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:33</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6102&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>82bf4faf5ded6db465c0745defc3930a696e88d4d33ddf0f210ccd0de0777097</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6103</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Sachaca, de Sachaca</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2988.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1236,76 +1068,76 @@
 Zonas afectadas: Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:34</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6103&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>f0d91a010a540a1e80128ca22b7b8d75f685b3faedf907a0db23e1bbef52a91a</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6104</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10337.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1315,76 +1147,76 @@
 Zonas afectadas: Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:34</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6104&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>51490abb4e2fdad5b9baa4104f7c32f8304c90ecf9bae88db576055162e3d58f</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6105</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1294.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1394,76 +1226,76 @@
 Zonas afectadas: Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:35 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:35</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6105&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>7d988d85147c853dabc84fee8bb12cdaaec86331eb4eeab6bc9be34c7b81d6db</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6106</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Paucarpata, de Paucarpata</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2273.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1473,80 +1305,80 @@
 Zonas afectadas: Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6106&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>0dc0b5a6576d0ca862495ca0bfc716c87f0654909fb6561e21a349396ebb9314</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6112</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>21/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Colina desde REC - 950145.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIERCOLES, 21 DE OCTUBRE DE 2026:
@@ -1557,80 +1389,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:39</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6112&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>d9bf4e25cfee750fde0f10344839c63569afbe87d18cfd10c7e21f86c8d3b099</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6111</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>21/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : [808] AUTOPISTA.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 21 DE OCTUBRE DE 2026:
@@ -1641,76 +1473,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6111&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>f6de992ab89cef5ca98439ac389dca9ca1b0e896e777db0f9dbe1f408f5f432f</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6110</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>05:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3586.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1720,76 +1552,76 @@
 Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6107</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3645.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1799,76 +1631,76 @@
 Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6108</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3553.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1878,76 +1710,76 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6109</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Mariano Melgar, de Mariano Melgar</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero de distribución.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3079.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1957,30 +1789,30 @@
 Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>ad4ee179ccca6b22909b8028d1f8384fb511a972f6d5fe5349c30ebfc3a17fb7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18"/>
+  <autoFilter ref="A1:P16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2021,7 +1853,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 13:45:50</t>
+          <t>2026-10-18 14:03:01</t>
         </is>
       </c>
     </row>
@@ -2045,7 +1877,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2057,7 +1889,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -2069,7 +1901,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
     </row>
@@ -2141,7 +1973,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2000,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 14:03:01</t>
+          <t>2026-10-19 16:59:48</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P16" headerRowCount="1">
-  <autoFilter ref="A1:P16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,392 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mollendo, de Mollendo</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.</t>
+          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+          <t>Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : La Florida desde REC - 200284.</t>
+          <t>Circuito : Pitay desde CC - 950326.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>REFORZAMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
+          <t>6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-DOMINGO, 18 DE OCTUBRE DE 2026:
-Circuito : La Florida desde REC - 200284.
-Hora : 07:00 a 16:00 Hrs.
-Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: 7 de Junio, El Mirador Al Pacifico, La Florida, La Victoria, Las Ambarinas, Las Antenas, Luz y Fuerza, Nueva Generación, Nuevo Peru, Progreso, Villa Lourdes 1 Etapa, Villa Lourdes 2 Etapa, Zona Industrial Municipal.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8063, 8004, 8256, 8072, 8056, 8055, 8065, 8459, 8281, 8067, 8066, 8068, 8069, 8071, 8374, 8064, 8226, 8579, 8745, 8073.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 11:51</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6097&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>6fed2ddd39cb04f2c4bb410d074ab0e70f77fcd95df52f708e0f9f58b8dd3f9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Alto Bellavista, Alto San Martin, Apvis Los Olivos del Puerto, Bellavista, Los Pinos, Obreros Municipales, San Martin, Villa Lourdes 2 Etapa, Villa Magisterial.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Hospital desde REC - 200136.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-DOMINGO, 18 DE OCTUBRE DE 2026:
-Circuito : Hospital desde REC - 200136.
-Hora : 07:00 a 16:00 Hrs.
-Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Alto Bellavista, Alto San Martin, Apvis Los Olivos del Puerto, Bellavista, Los Pinos, Obreros Municipales, San Martin, Villa Lourdes 2 Etapa, Villa Magisterial.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8083, 8082, 8084, 8075, 8589, 8077, 8078, 8076, 8081, 8588, 8074, 8391, 8080, 8079, 10296, 8333, 8381, 8407, 8690, 8336, 8349, 8572, 10030.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 11:51 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 11:51</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6098&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>58ebc0a7d301f082487a4adfea231c5b196f4d9f9d3c6d720aa29dff4cb18ff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Aptasa, Centro Comercial Las Malvinas, Cooperativa Ex San Jose Obrero, La Cuarentenaria, Parque Industrial Rio Seco, Rio Seco, Santa Maria.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de equipo de maniobra.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Rio Seco desde BC - 080104.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 18 DE OCTUBRE DE 2026:
-Circuito : Rio Seco desde BC - 080104.
-Hora : 08:00 a 10:00 Hrs.
-Motivo : Cambio de equipo de maniobra.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Aptasa, Centro Comercial Las Malvinas, Cooperativa Ex San Jose Obrero, La Cuarentenaria, Parque Industrial Rio Seco, Rio Seco, Santa Maria.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5814, 2034, 1492, 3367, 2670, 3607, 10218, 5335, 2544, 2687, 3383, 5637, 5334, 5685, 1897, 4972, 1978, 2642, 5326, 1386, 2641, 3773, 3948, 3725, 2226, 4175, 4303, 4304, 1940, 4487, 4489, 4557, 4899, 4990, 3462, 5166, 5035, 5053, 5342, 5344, 5343, 5580, 5581, 5392, 5634, 5638, 5672, 5200, 5790, 5770, 2643, 10213, 4001, 10285, 5898.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 10:42 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 10:42</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6096&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6c883ab253447b80dcc88768cfd341fa0fc228dafdb7c7a7142fbe273754f333</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6099</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>18/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Apiamo, Bellavista, Catarindo, Centenario, Cercado de Mollendo, Estibadores, Inclán, La Florida, Los Delfines de Mollendo, Los Tres Portales, San Agustín Arvidunsa, Señor del Rímac.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento del transformador de potencia y line de transmisión.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEA : [L-3031] BASE ISLAY-MOLLENDO. SET : [31] MOLLENDO.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 18 DE OCTUBRE DE 2026:
-LÍNEA : [L-3031] BASE ISLAY-MOLLENDO.
-SET : [31] MOLLENDO.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento del transformador de potencia y line de transmisión.
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Apiamo, Bellavista, Catarindo, Centenario, Cercado de Mollendo, Estibadores, Inclán, La Florida, Los Delfines de Mollendo, Los Tres Portales, San Agustín Arvidunsa, Señor del Rímac.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8062, 8255, 8054, 8057, 8053, 8000, 8058, 8030, 8042, 8233, 8010, 8009, 8013, 8015, 8016, 8018, 8019, 8023, 8024, 8025, 8031, 8026, 8003, 8001, 8033, 8021, 8045, 8050, 8051, 8052, 8047, 8046, 8262, 8269, 8006, 8287, 8032, 8011, 8022, 8027, 8002, 8028, 8048, 8049, 8034, 8005, 8343, 8368, 8369, 8403, 8404, 8409, 8417, 8420, 8446, 8445, 8458, 8437, 8461, 8462, 8487, 8488, 8566, 8477, 8500, 8501, 8562, 8576, 8578, 8476, 8603, 8608, 8635, 8640, 8606, 8714, 8029, 8390, 8408, 8428, 8540.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 11:52 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 11:52</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6099&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>f8cb4dbbf73699c5cdb55ac77b37a3a9884ec3cd179f77f5387f54c689405d3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6102</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pitay desde CC - 950326.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026:
@@ -989,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:33 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:33</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6102&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>82bf4faf5ded6db465c0745defc3930a696e88d4d33ddf0f210ccd0de0777097</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6103</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Sachaca, de Sachaca</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2988.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1068,76 +731,76 @@
 Zonas afectadas: Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:34</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6103&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>f0d91a010a540a1e80128ca22b7b8d75f685b3faedf907a0db23e1bbef52a91a</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6104</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10337.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1147,76 +810,76 @@
 Zonas afectadas: Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:34</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6104&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>51490abb4e2fdad5b9baa4104f7c32f8304c90ecf9bae88db576055162e3d58f</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6105</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1294.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1226,76 +889,76 @@
 Zonas afectadas: Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:35 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:35</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6105&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>7d988d85147c853dabc84fee8bb12cdaaec86331eb4eeab6bc9be34c7b81d6db</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6106</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Paucarpata, de Paucarpata</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2273.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 20 DE OCTUBRE DE 2026.
@@ -1305,80 +968,80 @@
 Zonas afectadas: Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6106&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>0dc0b5a6576d0ca862495ca0bfc716c87f0654909fb6561e21a349396ebb9314</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6112</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>21/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Colina desde REC - 950145.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIERCOLES, 21 DE OCTUBRE DE 2026:
@@ -1389,80 +1052,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:39</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6112&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>d9bf4e25cfee750fde0f10344839c63569afbe87d18cfd10c7e21f86c8d3b099</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6111</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>21/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : [808] AUTOPISTA.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 21 DE OCTUBRE DE 2026:
@@ -1473,76 +1136,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6111&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>f6de992ab89cef5ca98439ac389dca9ca1b0e896e777db0f9dbe1f408f5f432f</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6110</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>05:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3586.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1552,76 +1215,76 @@
 Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6107</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3645.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1631,76 +1294,76 @@
 Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6108</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3553.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1710,76 +1373,76 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6109</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Mariano Melgar, de Mariano Melgar</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero de distribución.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3079.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1789,30 +1452,30 @@
 Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>ad4ee179ccca6b22909b8028d1f8384fb511a972f6d5fe5349c30ebfc3a17fb7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P16"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1853,7 +1516,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 16:59:48</t>
+          <t>2026-10-20 15:08:16</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1552,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1564,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1636,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1663,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P23" headerRowCount="1">
+  <autoFilter ref="A1:P23"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1474,8 +1474,912 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de seccionadores y transferencia de carga.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cercado desde REC - 200285.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Cercado desde REC - 200285.
+Hora : 06:00 a 09:00 Hrs.
+Motivo : Cambio de seccionadores y transferencia de carga.
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:50</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6117&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>03cea57f3fe74df27f3820d985267b4546a650595be786dfd8d42ad2551080d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6118</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de seccionadores y transferencia de carga.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Inclan desde SF6-3 - 200144.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Inclan desde SF6-3 - 200144.
+Hora : 06:00 a 09:00 Hrs.
+Motivo : Cambio de seccionadores y transferencia de carga.
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Miramar.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6118&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>cb1e674c184819a66945a4ba5bb84c420904a643d215ecebb46d57b6ce92dcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Modulo E Sector 1.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pitay desde CC - 200257.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8963, 8515, 8516, 8517, 8518</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Pitay desde CC - 200257.
+Hora : 07:05 a 15:05 Hrs.
+Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Modulo E Sector 1.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8963, 8515, 8516, 8517, 8518</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:45 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:45</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6113&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>11f02c5748bbaa17f58b7be100a129e3fb29db1f99b6d2ae1927249d09f3bf87</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Nueva Ciudad de Majes - Modulo A.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pitay desde CC - 950318.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Pitay desde CC - 950318.
+Hora : 07:05 a 15:05 Hrs.
+Motivo : Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Majes: Nueva Ciudad de Majes - Modulo A.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:47 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:47</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6114&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>a46f32770f07d4464e274d6cf56c5a9bc27180d57527bdf8240e8310d119b72d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Characato, Chiguata, Paucarpata, San Juan de Tarucani, de Characato, de Chiguata, de Paucarpata, de San Juan de Tarucani</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Characato: Mosopuquio. Urbanizaciones de distrito de Chiguata: Agua Salada, Anexo Cangallo, Anexo Cari Cari, Anexo La Rinconada, Anexo Quillocona, Anexo Villa Santa Maria, Buena Vista, Cacayaco, Cerrito Benavente, Chiguata, Collamarca, Contune, El Arenal, Espiritu Santo, Irrigacion Santa Maria II, La Bedoya, La Capilla, Miraflores, Tilumpaya, Villa Encanto. Urbanizaciones del distrito de Paucarpata: Santo Domingo y San Bernardo. Urbanizaciones del distrito de San Juan de Tarucani: Salinas Huito, San Juan de Tarucani.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión (reubicación de línea, conexión de pozos a tierra).</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [508] CHIGUATA.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : [508] CHIGUATA.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de las redes de media tensión (reubicación de línea, conexión de pozos a tierra).
+Zonas afectadas: Urbanizaciones del distrito de Characato: Mosopuquio. Urbanizaciones de distrito de Chiguata: Agua Salada, Anexo Cangallo, Anexo Cari Cari, Anexo La Rinconada, Anexo Quillocona, Anexo Villa Santa Maria, Buena Vista, Cacayaco, Cerrito Benavente, Chiguata, Collamarca, Contune, El Arenal, Espiritu Santo, Irrigacion Santa Maria II, La Bedoya, La Capilla, Miraflores, Tilumpaya, Villa Encanto. Urbanizaciones del distrito de Paucarpata: Santo Domingo y San Bernardo. Urbanizaciones del distrito de San Juan de Tarucani: Salinas Huito, San Juan de Tarucani.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:48 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:48</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6115&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>37b280639274f6095905470036ba4208547caebefea6b16852fbfcfdc49abd35</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, Miraflores</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito Arequipa: Ampliacion La Negrita, Cesar Vallejo, La Victoria, Miraflores. Urbanizaciones del distrito Miraflores: Miraflores.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Miraflores desde BC - 204004.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Miraflores desde BC - 204004.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito Arequipa: Ampliacion La Negrita, Cesar Vallejo, La Victoria, Miraflores. Urbanizaciones del distrito Miraflores: Miraflores.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:49 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:49</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6116&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>a85be54d55ddd9f98b1e594df5e3849e9bc6fd670b60407858faa149381616a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de cables de fuerza del transformador.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1488.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026.
+Circuito : SED 1488.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de cables de fuerza del transformador.
+Zonas afectadas: Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:52 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:52</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6120&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>29df7d1bcbed680a85456fae3392f5d7130aa91c0b42af28e5e6f78a683ad0e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Dean Valdivia, de Dean Valdivia</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Dean Valdivia: Alto Ensenada, Estacion La Ensenada, Irrigación Iberia, Villa Paraiso.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ensenada desde REC - 200147.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026:
+Circuito : Ensenada desde REC - 200147.
+Hora : 09:00 a 15:00 Hrs.
+Motivo : Mantenimiento de las redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Dean Valdivia: Alto Ensenada, Estacion La Ensenada, Irrigación Iberia, Villa Paraiso.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:51 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6119&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>033a6fc53c4481834f0acf4e826ad990c63ec5845a49e866e9903f9a80b9e278</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5138.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026.
+Circuito : SED 5138.
+Hora : 10:40 a 11:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:53</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6121&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>aaef47c2bd6c253e7e41e1b47833bc9c6545db3d724c829b1e40958e3f2e8096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>6122</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5812</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026.
+Circuito : SED 5812.
+Hora : 11:30 a 11:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:53</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6122&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>8a69c39c9eeaec588bf18b7512f88481cf8d135817c565c9400eb176c809fbd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>6123</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1893</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 23 DE OCTUBRE DE 2026.
+Circuito : SED 1893.
+Hora : 12:10 a 12:30 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:54 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:54</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6123&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>13908c5319006cd54a4381b7198e61d14aa346b6123207d97c5e2ca02ff9786e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1516,7 +2420,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 15:08:16</t>
+          <t>2026-10-21 15:18:53</t>
         </is>
       </c>
     </row>
@@ -1540,7 +2444,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -1552,7 +2456,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1564,7 +2468,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
@@ -1612,7 +2516,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1624,7 +2528,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1636,7 +2540,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1663,7 +2567,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P23" headerRowCount="1">
-  <autoFilter ref="A1:P23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
+  <autoFilter ref="A1:P18"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,455 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.</t>
+          <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).</t>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pitay desde CC - 950326.</t>
+          <t>Circuito : La Colina desde REC - 950145.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
+          <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 20 DE OCTUBRE DE 2026:
-Circuito : Pitay desde CC - 950326.
-Hora : 07:05 a 15:05 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de terminales, limpieza de aisladores, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Majes: Ciudad de Majes Modulo B Sector 2, Ciudad de Majes Modulo F, El Paraiso, Modulo E Sector 2, Nuevo Horizonte.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6511, 6513, 6507, 6502, 6512, 6503, 8970, 8971, 8972, 8526, 8760, 8761, 8762.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:33 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:33</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6102&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>82bf4faf5ded6db465c0745defc3930a696e88d4d33ddf0f210ccd0de0777097</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6103</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Sachaca, de Sachaca</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2988.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 20 DE OCTUBRE DE 2026.
-Circuito : SED 2988.
-Hora : 08:30 a 08:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Fundo Santa Rosa, Mz. A de Urb. Pampa de Camarones (Distrito de Sachaca).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:34</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6103&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>f0d91a010a540a1e80128ca22b7b8d75f685b3faedf907a0db23e1bbef52a91a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6104</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 10337.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 20 DE OCTUBRE DE 2026.
-Circuito : SED 10337.
-Hora : 11:00 a 11:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. B-C-D-E-F-G-J de Urb. San Basilio (Distrito de Jose Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:34 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:34</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6104&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>51490abb4e2fdad5b9baa4104f7c32f8304c90ecf9bae88db576055162e3d58f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6105</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1294.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 20 DE OCTUBRE DE 2026.
-Circuito : SED 1294.
-Hora : 11:50 a 12:10 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. A-B-D-F-G de Urb. Alvarez Thomas (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:35 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:35</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6105&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>7d988d85147c853dabc84fee8bb12cdaaec86331eb4eeab6bc9be34c7b81d6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6106</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Paucarpata, de Paucarpata</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2273.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 20 DE OCTUBRE DE 2026.
-Circuito : SED 2273.
-Hora : 14:00 a 14:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. K-N-Ñ-Q-R de Urb. Santo Domingo y San Bernardo (Distrito de Paucarpata).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:36</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6106&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0dc0b5a6576d0ca862495ca0bfc716c87f0654909fb6561e21a349396ebb9314</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6112</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : La Colina desde REC - 950145.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIERCOLES, 21 DE OCTUBRE DE 2026:
@@ -1052,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:39</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6112&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>d9bf4e25cfee750fde0f10344839c63569afbe87d18cfd10c7e21f86c8d3b099</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6111</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>21/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [808] AUTOPISTA.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 21 DE OCTUBRE DE 2026:
@@ -1136,76 +736,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6111&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>f6de992ab89cef5ca98439ac389dca9ca1b0e896e777db0f9dbe1f408f5f432f</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6110</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>05:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3586.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1215,76 +815,76 @@
 Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6107</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3645.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1294,76 +894,76 @@
 Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6108</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3553.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1373,76 +973,76 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6109</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Mariano Melgar, de Mariano Melgar</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero de distribución.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3079.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1452,80 +1052,80 @@
 Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>ad4ee179ccca6b22909b8028d1f8384fb511a972f6d5fe5349c30ebfc3a17fb7</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6117</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cercado desde REC - 200285.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1536,80 +1136,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6117&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>03cea57f3fe74df27f3820d985267b4546a650595be786dfd8d42ad2551080d2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Inclan desde SF6-3 - 200144.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1620,80 +1220,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6118&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>cb1e674c184819a66945a4ba5bb84c420904a643d215ecebb46d57b6ce92dcaf</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6113</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Modulo E Sector 1.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 200257.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1704,80 +1304,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:45 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:45</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6113&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>11f02c5748bbaa17f58b7be100a129e3fb29db1f99b6d2ae1927249d09f3bf87</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6114</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Nueva Ciudad de Majes - Modulo A.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 950318.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1788,80 +1388,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:47 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:47</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6114&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>a46f32770f07d4464e274d6cf56c5a9bc27180d57527bdf8240e8310d119b72d</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6115</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Characato, Chiguata, Paucarpata, San Juan de Tarucani, de Characato, de Chiguata, de Paucarpata, de San Juan de Tarucani</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Characato: Mosopuquio. Urbanizaciones de distrito de Chiguata: Agua Salada, Anexo Cangallo, Anexo Cari Cari, Anexo La Rinconada, Anexo Quillocona, Anexo Villa Santa Maria, Buena Vista, Cacayaco, Cerrito Benavente, Chiguata, Collamarca, Contune, El Arenal, Espiritu Santo, Irrigacion Santa Maria II, La Bedoya, La Capilla, Miraflores, Tilumpaya, Villa Encanto. Urbanizaciones del distrito de Paucarpata: Santo Domingo y San Bernardo. Urbanizaciones del distrito de San Juan de Tarucani: Salinas Huito, San Juan de Tarucani.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (reubicación de línea, conexión de pozos a tierra).</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : [508] CHIGUATA.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1872,80 +1472,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:48 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:48</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6115&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>37b280639274f6095905470036ba4208547caebefea6b16852fbfcfdc49abd35</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6116</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Arequipa, Miraflores</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Arequipa: Ampliacion La Negrita, Cesar Vallejo, La Victoria, Miraflores. Urbanizaciones del distrito Miraflores: Miraflores.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Miraflores desde BC - 204004.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1956,76 +1556,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:49 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:49</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6116&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>a85be54d55ddd9f98b1e594df5e3849e9bc6fd670b60407858faa149381616a6</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6120</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de cables de fuerza del transformador.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1488.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -2035,80 +1635,80 @@
 Zonas afectadas: Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:52</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6120&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>29df7d1bcbed680a85456fae3392f5d7130aa91c0b42af28e5e6f78a683ad0e5</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6119</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Dean Valdivia, de Dean Valdivia</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Dean Valdivia: Alto Ensenada, Estacion La Ensenada, Irrigación Iberia, Villa Paraiso.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ensenada desde REC - 200147.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -2119,76 +1719,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:51</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6119&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>033a6fc53c4481834f0acf4e826ad990c63ec5845a49e866e9903f9a80b9e278</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6121</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>10:40</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5138.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -2198,76 +1798,76 @@
 Zonas afectadas: Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6121&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>aaef47c2bd6c253e7e41e1b47833bc9c6545db3d724c829b1e40958e3f2e8096</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>6122</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5812</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -2277,76 +1877,76 @@
 Zonas afectadas: Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6122&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>8a69c39c9eeaec588bf18b7512f88481cf8d135817c565c9400eb176c809fbd2</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>6123</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1893</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -2356,30 +1956,30 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:54 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:54</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6123&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>13908c5319006cd54a4381b7198e61d14aa346b6123207d97c5e2ca02ff9786e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2420,7 +2020,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:18:53</t>
+          <t>2026-10-22 15:19:45</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2044,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2056,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2068,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2140,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2167,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
-  <autoFilter ref="A1:P18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P23" headerRowCount="1">
+  <autoFilter ref="A1:P23"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,219 +593,51 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>San Juan de Siguas, Santa Isabel de Siguas, de San Juan de Siguas, de Santa Isabel de Siguas</t>
+          <t>Arequipa, de Arequipa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.</t>
+          <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+          <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : La Colina desde REC - 950145.</t>
+          <t>Circuito : SED 3586.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
-        </is>
-      </c>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MIERCOLES, 21 DE OCTUBRE DE 2026:
-Circuito : La Colina desde REC - 950145.
-Hora : 06:00 a 15:00 Hrs.
-Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
-Zonas afectadas: Urbanizaciones del distrito de San Juan de Siguas: Tambillo. Urbanizaciones del distrito de Santa Isabel de Siguas: Los Geranios, Santa Isabel de Siguas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6141, 6139, 6140, 6138, 6611, 6147, 6145, 6143, 6142, 6151, 6620, 6148, 8838, 6293, 6971, 6447, 6150, 10121, 6144, 6295, 6452, 6449, 6618, 7671, 7710, 8837, 8866, 8894, 6149, 8892, 8580, 8605.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:39 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:39</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6112&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>d9bf4e25cfee750fde0f10344839c63569afbe87d18cfd10c7e21f86c8d3b099</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6111</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [808] AUTOPISTA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 21 DE OCTUBRE DE 2026:
-Circuito : [808] AUTOPISTA.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: La Cabaña, Peruano-Argentino-Boliviano Zona II-III.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3984, 3854, 3871, 3806, 3897, 1838, 3705, 1349, 2464, 1829, 1837, 1836, 1839, 1841, 2685, 2684, 3789, 3889, 3887, 4025, 4027, 4026, 4080, 4202, 4233, 4234, 4221, 4239, 4290, 4289, 4291, 4462, 4476, 4477, 4543, 4653, 4753, 4949, 5032, 5007, 5174, 5169, 5270, 5263, 5375, 5410, 5422, 5586, 5601, 5584, 5515, 5407, 5628, 5602, 5408, 5170, 5745, 5783, 5784, 5786, 5798, 10172, 5988, 5989, 5990, 5991.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:38</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6111&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>f6de992ab89cef5ca98439ac389dca9ca1b0e896e777db0f9dbe1f408f5f432f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6110</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3586.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -815,76 +647,76 @@
 Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:38</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6107</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3645.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -894,76 +726,76 @@
 Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:36</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6108</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la subestación.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3553.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -973,76 +805,76 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16/10/2026 17:37</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6109</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>22/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Mariano Melgar, de Mariano Melgar</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de tablero de distribución.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3079.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 22 DE OCTUBRE DE 2026.
@@ -1052,80 +884,80 @@
 Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:37</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:47</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>ad4ee179ccca6b22909b8028d1f8384fb511a972f6d5fe5349c30ebfc3a17fb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5dd5dfa9bcc3551fa1eba97d57e3da0d9adb86d928eeaeec708f3e9d58278bc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6117</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cercado desde REC - 200285.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1136,80 +968,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6117&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>03cea57f3fe74df27f3820d985267b4546a650595be786dfd8d42ad2551080d2</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Inclan desde SF6-3 - 200144.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1220,80 +1052,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6118&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>cb1e674c184819a66945a4ba5bb84c420904a643d215ecebb46d57b6ce92dcaf</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6113</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Modulo E Sector 1.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 200257.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1304,80 +1136,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:45 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:45</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6113&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>11f02c5748bbaa17f58b7be100a129e3fb29db1f99b6d2ae1927249d09f3bf87</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6114</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Nueva Ciudad de Majes - Modulo A.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 950318.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1388,80 +1220,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:47 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:47</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6114&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>a46f32770f07d4464e274d6cf56c5a9bc27180d57527bdf8240e8310d119b72d</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6115</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Characato, Chiguata, Paucarpata, San Juan de Tarucani, de Characato, de Chiguata, de Paucarpata, de San Juan de Tarucani</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Characato: Mosopuquio. Urbanizaciones de distrito de Chiguata: Agua Salada, Anexo Cangallo, Anexo Cari Cari, Anexo La Rinconada, Anexo Quillocona, Anexo Villa Santa Maria, Buena Vista, Cacayaco, Cerrito Benavente, Chiguata, Collamarca, Contune, El Arenal, Espiritu Santo, Irrigacion Santa Maria II, La Bedoya, La Capilla, Miraflores, Tilumpaya, Villa Encanto. Urbanizaciones del distrito de Paucarpata: Santo Domingo y San Bernardo. Urbanizaciones del distrito de San Juan de Tarucani: Salinas Huito, San Juan de Tarucani.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (reubicación de línea, conexión de pozos a tierra).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : [508] CHIGUATA.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1472,80 +1304,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:48 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:48</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6115&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>37b280639274f6095905470036ba4208547caebefea6b16852fbfcfdc49abd35</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6116</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Arequipa, Miraflores</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Arequipa: Ampliacion La Negrita, Cesar Vallejo, La Victoria, Miraflores. Urbanizaciones del distrito Miraflores: Miraflores.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Miraflores desde BC - 204004.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1556,76 +1388,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:49 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:49</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6116&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>a85be54d55ddd9f98b1e594df5e3849e9bc6fd670b60407858faa149381616a6</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6120</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de cables de fuerza del transformador.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1488.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1635,80 +1467,80 @@
 Zonas afectadas: Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:52</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6120&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>29df7d1bcbed680a85456fae3392f5d7130aa91c0b42af28e5e6f78a683ad0e5</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6119</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Dean Valdivia, de Dean Valdivia</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Dean Valdivia: Alto Ensenada, Estacion La Ensenada, Irrigación Iberia, Villa Paraiso.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ensenada desde REC - 200147.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1719,76 +1551,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:51</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6119&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>033a6fc53c4481834f0acf4e826ad990c63ec5845a49e866e9903f9a80b9e278</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6121</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>10:40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5138.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1798,76 +1630,76 @@
 Zonas afectadas: Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6121&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>aaef47c2bd6c253e7e41e1b47833bc9c6545db3d724c829b1e40958e3f2e8096</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6122</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5812</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1877,76 +1709,76 @@
 Zonas afectadas: Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6122&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>8a69c39c9eeaec588bf18b7512f88481cf8d135817c565c9400eb176c809fbd2</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6123</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1893</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1956,30 +1788,617 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 21/10/2026 5:54 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2026 5:54</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6123&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>13908c5319006cd54a4381b7198e61d14aa346b6123207d97c5e2ca02ff9786e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Atiquipa, Yauca, de Atiquipa, de Yauca</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Agua Salada desde REC - 560244.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : Agua Salada desde REC - 560244.
+Hora : 07:00 a 16:00 Hrs.
+Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
+Zonas afectadas: Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:51 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:51</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6128&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>22e528689113c8e3ce1d6b17953326aaa72b2b0506319d4b91fa8b3122b0e6be</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Chala, de Chala</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Chala: Imperial La Aguadita.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Manuel Prado desde SF6 - 200173.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9869, 10257, 9983, 10166, 9798, 9382, 9404.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : Manuel Prado desde SF6 - 200173.
+Hora : 07:00 a 16:00 Hrs.
+Motivo : Instalación de nuevo equipo de protección y maniobra (recloser).
+Zonas afectadas: Urbanizaciones del distrito de Chala: Imperial La Aguadita.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9869, 10257, 9983, 10166, 9798, 9382, 9404.</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>el 21/10/2026 5:54 por Cuenta del sistema</t>
+          <t>el 23/10/2026 7:52 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21/10/2026 5:54</t>
+          <t>23/10/2026 7:52</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6123&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6129&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13908c5319006cd54a4381b7198e61d14aa346b6123207d97c5e2ca02ff9786e</t>
+          <t>9e01568692780ed3656d59b97dc44fb97c58e484e7d42e7b6bc9a9f610b1bb29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Pampamarca, de Pampamarca</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Pampamarca: Cochapampa, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cotahuasi desde CC - 700107.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>7320, 7321, 7322, 7752, 7750, 7749, 7751.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : Cotahuasi desde CC - 700107.
+Hora : 07:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión y podado de árboles.
+Zonas afectadas: Urbanizaciones del distrito de Pampamarca: Cochapampa, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7320, 7321, 7322, 7752, 7750, 7749, 7751.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:52 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:52</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6130&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>ef0fc2855ac971bfda56d518a9a34f4ce55f66e16bcce9a26e338863dd29136a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6124</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Lomas, de Lomas</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>PROVINCIA DE CARAVELÍ: Distrito de Lomas, Bella Unión, Acarí, Yauca, Jaquí, Atiquipa y Chala.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de las</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA : [6672] MARCONA - BELLA UNIÓN Y [6675] BELLA UNIÓN – CHALA. SET : [56] BELLA UNIÓN, [58] CHALA Y JAHUAY, [57] MARCONA (CELDA)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+LÍNEA : [6672] MARCONA - BELLA UNIÓN Y [6675] BELLA UNIÓN – CHALA.
+SET : [56] BELLA UNIÓN, [58] CHALA Y JAHUAY, [57] MARCONA (CELDA)
+Hora : 07:30 a 16:30 Hrs.
+Motivo : Mantenimiento de las subestaciones y líneas de transmisión.
+Las zonas afectadas por el corte programado serán:
+PROVINCIA DE CARAVELÍ:
+Distrito de Lomas, Bella Unión, Acarí, Yauca, Jaquí, Atiquipa y Chala.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:48 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:48</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6124&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>fe03af7f7d1e0f1fcbb5027f40dc199a1541ce5fd9e480d3642972205533620e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>6126</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, Yura, de Cerro Colorado, de Yura</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Ampliación Hijos Ciudad de Dios, Apiaar, Apima II La Alborada Cerro Colorado, Apipa Sector II, Apipa Sector III, Apipa Sector IV, Ciudad de Dios Zona 1, Granjeros Unidos I, Jose Luis Bustamante y Rivero, Los Camineros Empleados, Los Camineros Obreros, Nueva Juventud, Taller Monserrat, Taller Monserrat II Ampliación. Urbanizaciones del distrito de Yura: A.V. Villa Cristo, Ampliación Hijos Ciudad de Dios, Cap. Fap Jose Abelardo Quiñones, Ciudad de Dios Zona 1-2-3-4, Ciudad Municipal Zona 9, El Altiplano Sector 1 Zona A-B-C, El Altiplano Sector 2 Zona B, Elmer Faucett Profam Sector 1-2-3, Jose Abelardo Quiñonez II Etapa, Upis Los Milagros, Upis Los Milagros Zona I, Villa Los Milagros.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ciudad Municipal desde REC - 080216.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3932, 3469, 3470, 2126, 1878, 1877, 2095, 2222, 2097, 2096, 1778, 3154, 1879, 2765, 2764, 3155, 3156, 2092, 2855, 3594, 3593, 3496, 2088, 2089, 2774, 2775, 2091, 2087, 3770, 2090, 2086, 1987, 2779, 2776, 2781, 2777, 2778, 2780, 2854, 3426, 3407, 3408, 3409, 3410, 3411, 3401, 3402, 3656, 3657, 3658, 3687, 2174, 3794, 1876, 4015, 4051, 4127, 4148, 4147, 4131, 4130, 4287, 4339, 4470, 4438, 4540, 4621, 4671, 4670, 4472, 4684, 4718, 4719, 4744, 4816, 4811, 4845, 4846, 4847, 4778, 4777, 4779, 5143, 5144, 5145, 5087, 5103, 5104, 5148, 5147, 5149, 5150, 4758, 5197, 5391, 5430, 5433, 5431, 5432, 5434, 5435, 5436, 5437, 5449, 5554, 5555, 5556, 5558, 5559, 5557, 5560, 5561, 5562, 5563, 5564, 5606, 5642, 5699, 5700, 5774, 5826, 5850, 5827, 10046, 5931, 10122, 10016, 10017, 10019, 10018, 10015, 10259, 10292, 5912, 5913, 10353, 5748.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : Ciudad Municipal desde REC - 080216.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Ampliación Hijos Ciudad de Dios, Apiaar, Apima II La Alborada Cerro Colorado, Apipa Sector II, Apipa Sector III, Apipa Sector IV, Ciudad de Dios Zona 1, Granjeros Unidos I, Jose Luis Bustamante y Rivero, Los Camineros Empleados, Los Camineros Obreros, Nueva Juventud, Taller Monserrat, Taller Monserrat II Ampliación. Urbanizaciones del distrito de Yura: A.V. Villa Cristo, Ampliación Hijos Ciudad de Dios, Cap. Fap Jose Abelardo Quiñones, Ciudad de Dios Zona 1-2-3-4, Ciudad Municipal Zona 9, El Altiplano Sector 1 Zona A-B-C, El Altiplano Sector 2 Zona B, Elmer Faucett Profam Sector 1-2-3, Jose Abelardo Quiñonez II Etapa, Upis Los Milagros, Upis Los Milagros Zona I, Villa Los Milagros.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3932, 3469, 3470, 2126, 1878, 1877, 2095, 2222, 2097, 2096, 1778, 3154, 1879, 2765, 2764, 3155, 3156, 2092, 2855, 3594, 3593, 3496, 2088, 2089, 2774, 2775, 2091, 2087, 3770, 2090, 2086, 1987, 2779, 2776, 2781, 2777, 2778, 2780, 2854, 3426, 3407, 3408, 3409, 3410, 3411, 3401, 3402, 3656, 3657, 3658, 3687, 2174, 3794, 1876, 4015, 4051, 4127, 4148, 4147, 4131, 4130, 4287, 4339, 4470, 4438, 4540, 4621, 4671, 4670, 4472, 4684, 4718, 4719, 4744, 4816, 4811, 4845, 4846, 4847, 4778, 4777, 4779, 5143, 5144, 5145, 5087, 5103, 5104, 5148, 5147, 5149, 5150, 4758, 5197, 5391, 5430, 5433, 5431, 5432, 5434, 5435, 5436, 5437, 5449, 5554, 5555, 5556, 5558, 5559, 5557, 5560, 5561, 5562, 5563, 5564, 5606, 5642, 5699, 5700, 5774, 5826, 5850, 5827, 10046, 5931, 10122, 10016, 10017, 10019, 10018, 10015, 10259, 10292, 5912, 5913, 10353, 5748.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:50 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:50</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6126&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>f4484a88e3e1014dee411617dd499f90017ed1f3a3214c4a61cc8d6f3e634303</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, Tiabaya, Uchumayo, de Cerro Colorado, de Tiabaya, de Uchumayo</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Cerro Colorado: Irrigacion El Cural Lateral 8, Urbanizaciones del Distrito de Tiabaya: Alto Cerro Verde, El Arenal, El Nazareno, Frente Al Sol, La Molina, Virgen de Las Peñas Zona A-B, Virgen Las Peñas. Urbanizaciones del Distrito de Uchumayo: Cerro Verde, Congata, El Carmen de Congata I, El Carmen II, El Huayco, El Trebol de Uchumayo, Estacion de Uchumayo, Ignacio Alvares Thomas Sector I-II, Irrigacion El Cural Lateral 7, Los Diamantes, Nueva Leticia, Pan de Azucar, Pueblo Libre, Santa Teresa Zona A, Uchumayo.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de postes y armados de media tensión.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [1902] CONGATA.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3973, 3791, 2286, 3827, 3904, 3906, 1906, 1749, 2177, 2277, 3076, 1215, 2546, 1449, 2545, 3816, 3817, 3833, 3864, 3877, 3869, 1505, 2063, 1619, 1680, 3461, 2176, 1910, 3168, 1822, 1427, 3275, 3169, 2059, 2896, 2499, 1827, 2548, 2064, 1134, 1908, 1187, 2065, 1911, 3468, 3596, 1451, 3540, 3746, 2041, 1758, 2445, 2149, 1913, 1584, 3606, 3454, 1502, 3352, 3983, 1135, 3982, 4028, 3929, 1416, 4052, 4077, 4315, 4283, 4284, 4285, 4286, 4278, 4471, 4542, 4625, 4678, 4702, 4700, 4701, 3691, 4726, 4727, 4725, 4729, 4728, 4864, 4943, 4944, 5178, 5283, 5362, 5421, 5874, 5915, 5914, 10031, 10129, 10203, 10249, 1125, 1740, 3651, 1757, 4703, 2313, 5733, 2124, 5575, 5154, 5937.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : [1902] CONGATA.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de postes y armados de media tensión.
+Zonas afectadas: Urbanizaciones del Distrito de Cerro Colorado: Irrigacion El Cural Lateral 8,
+Urbanizaciones del Distrito de Tiabaya: Alto Cerro Verde, El Arenal, El Nazareno, Frente Al Sol, La Molina, Virgen de Las Peñas Zona A-B, Virgen Las Peñas. Urbanizaciones del Distrito de Uchumayo: Cerro Verde, Congata, El Carmen de Congata I, El Carmen II, El Huayco, El Trebol de Uchumayo, Estacion de Uchumayo, Ignacio Alvares Thomas Sector I-II, Irrigacion El Cural Lateral 7, Los Diamantes, Nueva Leticia, Pan de Azucar, Pueblo Libre, Santa Teresa Zona A, Uchumayo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3973, 3791, 2286, 3827, 3904, 3906, 1906, 1749, 2177, 2277, 3076, 1215, 2546, 1449, 2545, 3816, 3817, 3833, 3864, 3877, 3869, 1505, 2063, 1619, 1680, 3461, 2176, 1910, 3168, 1822, 1427, 3275, 3169, 2059, 2896, 2499, 1827, 2548, 2064, 1134, 1908, 1187, 2065, 1911, 3468, 3596, 1451, 3540, 3746, 2041, 1758, 2445, 2149, 1913, 1584, 3606, 3454, 1502, 3352, 3983, 1135, 3982, 4028, 3929, 1416, 4052, 4077, 4315, 4283, 4284, 4285, 4286, 4278, 4471, 4542, 4625, 4678, 4702, 4700, 4701, 3691, 4726, 4727, 4725, 4729, 4728, 4864, 4943, 4944, 5178, 5283, 5362, 5421, 5874, 5915, 5914, 10031, 10129, 10203, 10249, 1125, 1740, 3651, 1757, 4703, 2313, 5733, 2124, 5575, 5154, 5937.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:50 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:50</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6127&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>c805b5e2a87b231e670e03fec65d7802495e513dd6b6449719aad55f42686659</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>6125</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Arequipa: Parque Industrial.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la línea de media tensión.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [402] INCA TOPS.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1474, 2339, 2392, 1475, 1476, 1684, 1473, 1086, 3277, 2503, 4398, 5506, 5321, 10247, 5303.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 25 DE OCTUBRE DE 2026:
+Circuito : [402] INCA TOPS.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de la línea de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Arequipa: Parque Industrial.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1474, 2339, 2392, 1475, 1476, 1684, 1473, 1086, 3277, 2503, 4398, 5506, 5321, 10247, 5303.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>el 23/10/2026 7:49 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026 7:49</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6125&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1f85796a88820bbed9db1d0d57c177d29f72a6e4e541c55c76bab1c41af51a23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18"/>
+  <autoFilter ref="A1:P23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2020,7 +2439,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:19:45</t>
+          <t>2026-10-23 15:09:02</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2463,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2475,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2487,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2535,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2547,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2559,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2586,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P23" headerRowCount="1">
-  <autoFilter ref="A1:P23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P19" headerRowCount="1">
+  <autoFilter ref="A1:P19"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Arequipa, de Arequipa</t>
+          <t>Mollendo, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
+          <t>Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de posición del conmutador.</t>
+          <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 3586.</t>
+          <t>Circuito : Cercado desde REC - 200285.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,328 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 22 DE OCTUBRE DE 2026.
-Circuito : SED 3586.
-Hora : 05:00 a 05:30 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 1 de Calle San Camilo (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:38 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:38</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6110&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>fb73ff60d9ae470b2b3262b293e9ba8244c0cea20661a7edd60dcbb9565b6d10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urb. Los Sauces (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3645.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 22 DE OCTUBRE DE 2026.
-Circuito : SED 3645.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento de la subestación.
-Zonas afectadas: Urb. Los Sauces (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:36 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:36</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6107&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>cafa9d5ac06f777c5e4ff87263a039899e9fc2515e8385d1ddd5486150b6b49b</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6108</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la subestación.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3553.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 22 DE OCTUBRE DE 2026.
-Circuito : SED 3553.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento de la subestación.
-Zonas afectadas: Mz. A-B-C-D de Urb. Casabella (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:37</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6108&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>233ec5f38946c90b25a2d7280b000325de47b1a71366847c47b40c3ffb25ad2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6109</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Mariano Melgar, de Mariano Melgar</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de tablero de distribución.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3079.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 22 DE OCTUBRE DE 2026.
-Circuito : SED 3079.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de tablero de distribución.
-Zonas afectadas: Cuadra 8 de la Av. Perú, Cuadra 6-7 de Av. Nicolas de Pierola (Distrito de Mariano Melgar).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 16/10/2026 17:37 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23/10/2026 7:47</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6109&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5dd5dfa9bcc3551fa1eba97d57e3da0d9adb86d928eeaeec708f3e9d58278bc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6117</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Inclan, Los Delfines de Mollendo.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de seccionadores y transferencia de carga.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Cercado desde REC - 200285.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -968,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8029, 8030, 8034, 8032, 8233, 8033, 8420, 8437, 8042, 8501, 8031, 8603, 8368, 8428.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6117&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>03cea57f3fe74df27f3820d985267b4546a650595be786dfd8d42ad2551080d2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Miramar.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de seccionadores y transferencia de carga.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Inclan desde SF6-3 - 200144.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1052,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8038, 8037, 8382, 8036, 8470, 8039.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:50</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6118&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>cb1e674c184819a66945a4ba5bb84c420904a643d215ecebb46d57b6ce92dcaf</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6113</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Apurimeños En El Distrito de Majes, Modulo E Sector 1.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 200257.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1136,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8963, 8515, 8516, 8517, 8518</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:45 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:45</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6113&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>11f02c5748bbaa17f58b7be100a129e3fb29db1f99b6d2ae1927249d09f3bf87</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6114</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Nueva Ciudad de Majes - Modulo A.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (limpieza de aisladores, podado de árboles, subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pitay desde CC - 950318.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1220,80 +904,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6469, 6483, 6474, 6475, 6473, 6472, 10288.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:47 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:47</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6114&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>a46f32770f07d4464e274d6cf56c5a9bc27180d57527bdf8240e8310d119b72d</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6115</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Characato, Chiguata, Paucarpata, San Juan de Tarucani, de Characato, de Chiguata, de Paucarpata, de San Juan de Tarucani</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Characato: Mosopuquio. Urbanizaciones de distrito de Chiguata: Agua Salada, Anexo Cangallo, Anexo Cari Cari, Anexo La Rinconada, Anexo Quillocona, Anexo Villa Santa Maria, Buena Vista, Cacayaco, Cerrito Benavente, Chiguata, Collamarca, Contune, El Arenal, Espiritu Santo, Irrigacion Santa Maria II, La Bedoya, La Capilla, Miraflores, Tilumpaya, Villa Encanto. Urbanizaciones del distrito de Paucarpata: Santo Domingo y San Bernardo. Urbanizaciones del distrito de San Juan de Tarucani: Salinas Huito, San Juan de Tarucani.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión (reubicación de línea, conexión de pozos a tierra).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : [508] CHIGUATA.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1304,80 +988,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3027, 3028, 3029, 2138, 3077, 1890, 2103, 3357, 2137, 2136, 2168, 2144, 2037, 2376, 3949, 3951, 3953, 3950, 3952, 1859, 4206, 4250, 4261, 4260, 4264, 4266, 4265, 4267, 4541, 4223, 4224, 4658, 4715, 4769, 4936, 4959, 5050, 5305, 5307, 5365, 5364, 5652, 5702, 5687, 5782, 5599, 5801, 10042, 10184, 5306, 5308, 10193.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:48 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:48</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6115&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>37b280639274f6095905470036ba4208547caebefea6b16852fbfcfdc49abd35</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6116</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Arequipa, Miraflores</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Arequipa: Ampliacion La Negrita, Cesar Vallejo, La Victoria, Miraflores. Urbanizaciones del distrito Miraflores: Miraflores.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Miraflores desde BC - 204004.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1388,76 +1072,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2366, 1164, 3872, 1171, 2576, 3370, 1776, 3633, 2358, 3386, 1552, 1378, 4871, 3451, 2647, 1158, 4299, 4872, 5639, 5763, 2648.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:49 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:49</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6116&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>a85be54d55ddd9f98b1e594df5e3849e9bc6fd670b60407858faa149381616a6</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6120</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de cables de fuerza del transformador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1488.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1467,80 +1151,80 @@
 Zonas afectadas: Pasaje la Merced de Urb. Vallecito, Residencial Vallecito (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:52</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6120&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>29df7d1bcbed680a85456fae3392f5d7130aa91c0b42af28e5e6f78a683ad0e5</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6119</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Dean Valdivia, de Dean Valdivia</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Dean Valdivia: Alto Ensenada, Estacion La Ensenada, Irrigación Iberia, Villa Paraiso.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las redes de media tensión.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ensenada desde REC - 200147.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026:
@@ -1551,76 +1235,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8238, 8183, 8185, 8187, 8177, 10061, 8176, 8179, 8178, 8432, 8225, 8173, 8174, 8175, 8180, 8181, 8182, 8163, 8485, 8358, 8359, 8361, 8360, 8355, 8354, 8364, 8186, 8188, 8443, 10062, 8353, 8649, 8184, 10186.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:51</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6119&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>033a6fc53c4481834f0acf4e826ad990c63ec5845a49e866e9903f9a80b9e278</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6121</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>10:40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5138.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1630,76 +1314,76 @@
 Zonas afectadas: Sector IX-X de la Urb. Parque Industrial Provenir Arequipa (Distrito Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6121&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>aaef47c2bd6c253e7e41e1b47833bc9c6545db3d724c829b1e40958e3f2e8096</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6122</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5812</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1709,76 +1393,76 @@
 Zonas afectadas: Mz. A-B-C de Urb. PPPJJ De Villa San Juan (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:53 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:53</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6122&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>8a69c39c9eeaec588bf18b7512f88481cf8d135817c565c9400eb176c809fbd2</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6123</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>23/10/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1893</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 23 DE OCTUBRE DE 2026.
@@ -1788,80 +1472,80 @@
 Zonas afectadas: Mz. A-B-C-D de Urb. Villa Canteras (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 21/10/2026 5:54 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21/10/2026 5:54</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6123&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>13908c5319006cd54a4381b7198e61d14aa346b6123207d97c5e2ca02ff9786e</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6128</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Atiquipa, Yauca, de Atiquipa, de Yauca</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Agua Salada desde REC - 560244.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -1872,80 +1556,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:51 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:51</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6128&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>22e528689113c8e3ce1d6b17953326aaa72b2b0506319d4b91fa8b3122b0e6be</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6129</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Chala, de Chala</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Chala: Imperial La Aguadita.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Instalación de nuevo equipo de protección y maniobra (recloser).</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : Manuel Prado desde SF6 - 200173.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>9869, 10257, 9983, 10166, 9798, 9382, 9404.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -1956,80 +1640,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9869, 10257, 9983, 10166, 9798, 9382, 9404.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:52</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6129&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>9e01568692780ed3656d59b97dc44fb97c58e484e7d42e7b6bc9a9f610b1bb29</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6130</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Pampamarca, de Pampamarca</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Pampamarca: Cochapampa, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión y podado de árboles.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cotahuasi desde CC - 700107.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>7320, 7321, 7322, 7752, 7750, 7749, 7751.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -2040,76 +1724,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7320, 7321, 7322, 7752, 7750, 7749, 7751.</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:52 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:52</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6130&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>ef0fc2855ac971bfda56d518a9a34f4ce55f66e16bcce9a26e338863dd29136a</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6124</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Lomas, de Lomas</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>PROVINCIA DE CARAVELÍ: Distrito de Lomas, Bella Unión, Acarí, Yauca, Jaquí, Atiquipa y Chala.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de las</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : [6672] MARCONA - BELLA UNIÓN Y [6675] BELLA UNIÓN – CHALA. SET : [56] BELLA UNIÓN, [58] CHALA Y JAHUAY, [57] MARCONA (CELDA)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -2122,80 +1806,80 @@
 Distrito de Lomas, Bella Unión, Acarí, Yauca, Jaquí, Atiquipa y Chala.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:48 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:48</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6124&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>fe03af7f7d1e0f1fcbb5027f40dc199a1541ce5fd9e480d3642972205533620e</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>6126</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, Yura, de Cerro Colorado, de Yura</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Ampliación Hijos Ciudad de Dios, Apiaar, Apima II La Alborada Cerro Colorado, Apipa Sector II, Apipa Sector III, Apipa Sector IV, Ciudad de Dios Zona 1, Granjeros Unidos I, Jose Luis Bustamante y Rivero, Los Camineros Empleados, Los Camineros Obreros, Nueva Juventud, Taller Monserrat, Taller Monserrat II Ampliación. Urbanizaciones del distrito de Yura: A.V. Villa Cristo, Ampliación Hijos Ciudad de Dios, Cap. Fap Jose Abelardo Quiñones, Ciudad de Dios Zona 1-2-3-4, Ciudad Municipal Zona 9, El Altiplano Sector 1 Zona A-B-C, El Altiplano Sector 2 Zona B, Elmer Faucett Profam Sector 1-2-3, Jose Abelardo Quiñonez II Etapa, Upis Los Milagros, Upis Los Milagros Zona I, Villa Los Milagros.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (subsanación de deficiencias en media tensión).</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde REC - 080216.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>3932, 3469, 3470, 2126, 1878, 1877, 2095, 2222, 2097, 2096, 1778, 3154, 1879, 2765, 2764, 3155, 3156, 2092, 2855, 3594, 3593, 3496, 2088, 2089, 2774, 2775, 2091, 2087, 3770, 2090, 2086, 1987, 2779, 2776, 2781, 2777, 2778, 2780, 2854, 3426, 3407, 3408, 3409, 3410, 3411, 3401, 3402, 3656, 3657, 3658, 3687, 2174, 3794, 1876, 4015, 4051, 4127, 4148, 4147, 4131, 4130, 4287, 4339, 4470, 4438, 4540, 4621, 4671, 4670, 4472, 4684, 4718, 4719, 4744, 4816, 4811, 4845, 4846, 4847, 4778, 4777, 4779, 5143, 5144, 5145, 5087, 5103, 5104, 5148, 5147, 5149, 5150, 4758, 5197, 5391, 5430, 5433, 5431, 5432, 5434, 5435, 5436, 5437, 5449, 5554, 5555, 5556, 5558, 5559, 5557, 5560, 5561, 5562, 5563, 5564, 5606, 5642, 5699, 5700, 5774, 5826, 5850, 5827, 10046, 5931, 10122, 10016, 10017, 10019, 10018, 10015, 10259, 10292, 5912, 5913, 10353, 5748.</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -2206,80 +1890,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3932, 3469, 3470, 2126, 1878, 1877, 2095, 2222, 2097, 2096, 1778, 3154, 1879, 2765, 2764, 3155, 3156, 2092, 2855, 3594, 3593, 3496, 2088, 2089, 2774, 2775, 2091, 2087, 3770, 2090, 2086, 1987, 2779, 2776, 2781, 2777, 2778, 2780, 2854, 3426, 3407, 3408, 3409, 3410, 3411, 3401, 3402, 3656, 3657, 3658, 3687, 2174, 3794, 1876, 4015, 4051, 4127, 4148, 4147, 4131, 4130, 4287, 4339, 4470, 4438, 4540, 4621, 4671, 4670, 4472, 4684, 4718, 4719, 4744, 4816, 4811, 4845, 4846, 4847, 4778, 4777, 4779, 5143, 5144, 5145, 5087, 5103, 5104, 5148, 5147, 5149, 5150, 4758, 5197, 5391, 5430, 5433, 5431, 5432, 5434, 5435, 5436, 5437, 5449, 5554, 5555, 5556, 5558, 5559, 5557, 5560, 5561, 5562, 5563, 5564, 5606, 5642, 5699, 5700, 5774, 5826, 5850, 5827, 10046, 5931, 10122, 10016, 10017, 10019, 10018, 10015, 10259, 10292, 5912, 5913, 10353, 5748.</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:50</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6126&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>f4484a88e3e1014dee411617dd499f90017ed1f3a3214c4a61cc8d6f3e634303</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>6127</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, Tiabaya, Uchumayo, de Cerro Colorado, de Tiabaya, de Uchumayo</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cerro Colorado: Irrigacion El Cural Lateral 8, Urbanizaciones del Distrito de Tiabaya: Alto Cerro Verde, El Arenal, El Nazareno, Frente Al Sol, La Molina, Virgen de Las Peñas Zona A-B, Virgen Las Peñas. Urbanizaciones del Distrito de Uchumayo: Cerro Verde, Congata, El Carmen de Congata I, El Carmen II, El Huayco, El Trebol de Uchumayo, Estacion de Uchumayo, Ignacio Alvares Thomas Sector I-II, Irrigacion El Cural Lateral 7, Los Diamantes, Nueva Leticia, Pan de Azucar, Pueblo Libre, Santa Teresa Zona A, Uchumayo.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Cambio de postes y armados de media tensión.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Circuito : [1902] CONGATA.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>3973, 3791, 2286, 3827, 3904, 3906, 1906, 1749, 2177, 2277, 3076, 1215, 2546, 1449, 2545, 3816, 3817, 3833, 3864, 3877, 3869, 1505, 2063, 1619, 1680, 3461, 2176, 1910, 3168, 1822, 1427, 3275, 3169, 2059, 2896, 2499, 1827, 2548, 2064, 1134, 1908, 1187, 2065, 1911, 3468, 3596, 1451, 3540, 3746, 2041, 1758, 2445, 2149, 1913, 1584, 3606, 3454, 1502, 3352, 3983, 1135, 3982, 4028, 3929, 1416, 4052, 4077, 4315, 4283, 4284, 4285, 4286, 4278, 4471, 4542, 4625, 4678, 4702, 4700, 4701, 3691, 4726, 4727, 4725, 4729, 4728, 4864, 4943, 4944, 5178, 5283, 5362, 5421, 5874, 5915, 5914, 10031, 10129, 10203, 10249, 1125, 1740, 3651, 1757, 4703, 2313, 5733, 2124, 5575, 5154, 5937.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -2291,80 +1975,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3973, 3791, 2286, 3827, 3904, 3906, 1906, 1749, 2177, 2277, 3076, 1215, 2546, 1449, 2545, 3816, 3817, 3833, 3864, 3877, 3869, 1505, 2063, 1619, 1680, 3461, 2176, 1910, 3168, 1822, 1427, 3275, 3169, 2059, 2896, 2499, 1827, 2548, 2064, 1134, 1908, 1187, 2065, 1911, 3468, 3596, 1451, 3540, 3746, 2041, 1758, 2445, 2149, 1913, 1584, 3606, 3454, 1502, 3352, 3983, 1135, 3982, 4028, 3929, 1416, 4052, 4077, 4315, 4283, 4284, 4285, 4286, 4278, 4471, 4542, 4625, 4678, 4702, 4700, 4701, 3691, 4726, 4727, 4725, 4729, 4728, 4864, 4943, 4944, 5178, 5283, 5362, 5421, 5874, 5915, 5914, 10031, 10129, 10203, 10249, 1125, 1740, 3651, 1757, 4703, 2313, 5733, 2124, 5575, 5154, 5937.</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:50 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:50</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6127&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>c805b5e2a87b231e670e03fec65d7802495e513dd6b6449719aad55f42686659</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>6125</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Arequipa: Parque Industrial.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea de media tensión.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Circuito : [402] INCA TOPS.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1474, 2339, 2392, 1475, 1476, 1684, 1473, 1086, 3277, 2503, 4398, 5506, 5321, 10247, 5303.</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 25 DE OCTUBRE DE 2026:
@@ -2375,30 +2059,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1474, 2339, 2392, 1475, 1476, 1684, 1473, 1086, 3277, 2503, 4398, 5506, 5321, 10247, 5303.</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>el 23/10/2026 7:49 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>23/10/2026 7:49</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6125&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>1f85796a88820bbed9db1d0d57c177d29f72a6e4e541c55c76bab1c41af51a23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2439,7 +2123,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 15:09:02</t>
+          <t>2026-10-24 14:02:04</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2147,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2159,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2171,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2243,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2270,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
